--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。施設・居住系の画面から先へ進めない件の切り分けを7項目で示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項4件を含む</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2985,19 +2985,19 @@
       <c r="A93" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,136 +3210,211 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_追加調査報告書.xlsx</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>追加で実施した調査の報告</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr"/>
-      <c r="E105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106" ht="26" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr"/>
+      <c r="E108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109" ht="26" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B106" s="6" t="n">
+      <c r="B109" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="inlineStr"/>
-      <c r="E106" s="7" t="inlineStr"/>
-    </row>
-    <row r="107" ht="26" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="n">
-        <v>44</v>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr"/>
-      <c r="E107" s="7" t="inlineStr"/>
-    </row>
-    <row r="108" ht="26" customHeight="1">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>納品時又は求めに応じて提出する</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr"/>
-      <c r="E108" s="7" t="inlineStr"/>
-    </row>
-    <row r="109" ht="26" customHeight="1">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>本業務の成果品ではない</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr"/>
     </row>
     <row r="110" ht="26" customHeight="1">
-      <c r="A110" s="12" t="inlineStr">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>お諮りする内容である旨を明示して送付する</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr"/>
+      <c r="E110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111" ht="26" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>納品時又は求めに応じて提出する</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr"/>
+      <c r="E111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr"/>
+      <c r="E112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B110" s="13" t="n">
-        <v>98</v>
-      </c>
-      <c r="C110" s="14" t="inlineStr"/>
-      <c r="D110" s="14" t="inlineStr"/>
-      <c r="E110" s="14" t="inlineStr"/>
-    </row>
-    <row r="112" ht="76" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
+      <c r="B113" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="C113" s="14" t="inlineStr"/>
+      <c r="D113" s="14" t="inlineStr"/>
+      <c r="E113" s="14" t="inlineStr"/>
+    </row>
+    <row r="115" ht="76" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3349,8 +3424,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A115:E115"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費を新たに算定した。決着していない事項は過年度の数値を据え置き、何をどう置いたかを20件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項4件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1460,19 +1460,19 @@
       <c r="A32" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
+          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1485,19 +1485,19 @@
       <c r="A33" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
+          <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1560,19 +1560,19 @@
       <c r="A36" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
+          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
+          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1635,19 +1635,19 @@
       <c r="A39" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1685,19 +1685,19 @@
       <c r="A41" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1810,19 +1810,19 @@
       <c r="A46" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1885,19 +1885,19 @@
       <c r="A49" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1960,19 +1960,19 @@
       <c r="A52" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1985,19 +1985,19 @@
       <c r="A53" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2110,19 +2110,19 @@
       <c r="A58" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2160,19 +2160,19 @@
       <c r="A60" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2285,19 +2285,19 @@
       <c r="A65" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2310,19 +2310,19 @@
       <c r="A66" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2360,19 +2360,19 @@
       <c r="A68" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2385,19 +2385,19 @@
       <c r="A69" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2660,19 +2660,19 @@
       <c r="A80" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2885,19 +2885,19 @@
       <c r="A89" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2985,19 +2985,19 @@
       <c r="A93" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,136 +3285,186 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr"/>
-      <c r="E108" s="4" t="inlineStr"/>
-    </row>
-    <row r="109" ht="26" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="D110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111" ht="26" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B109" s="6" t="n">
+      <c r="B111" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C111" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr"/>
-      <c r="E109" s="7" t="inlineStr"/>
-    </row>
-    <row r="110" ht="26" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr"/>
-      <c r="E110" s="7" t="inlineStr"/>
-    </row>
-    <row r="111" ht="26" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr"/>
       <c r="E111" s="7" t="inlineStr"/>
     </row>
     <row r="112" ht="26" customHeight="1">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B112" s="6" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr"/>
       <c r="E112" s="7" t="inlineStr"/>
     </row>
     <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="12" t="inlineStr">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>納品時又は求めに応じて提出する</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr"/>
+      <c r="E113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114" ht="26" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr"/>
+      <c r="E114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115" ht="26" customHeight="1">
+      <c r="A115" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B113" s="13" t="n">
-        <v>101</v>
-      </c>
-      <c r="C113" s="14" t="inlineStr"/>
-      <c r="D113" s="14" t="inlineStr"/>
-      <c r="E113" s="14" t="inlineStr"/>
-    </row>
-    <row r="115" ht="76" customHeight="1">
-      <c r="A115" s="11" t="inlineStr">
+      <c r="B115" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="C115" s="14" t="inlineStr"/>
+      <c r="D115" s="14" t="inlineStr"/>
+      <c r="E115" s="14" t="inlineStr"/>
+    </row>
+    <row r="117" ht="76" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3424,8 +3474,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A117:E117"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1960,19 +1960,19 @@
       <c r="A52" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1985,19 +1985,19 @@
       <c r="A53" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2010,19 +2010,19 @@
       <c r="A54" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2185,19 +2185,19 @@
       <c r="A61" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2310,19 +2310,19 @@
       <c r="A66" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2335,19 +2335,19 @@
       <c r="A67" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2385,19 +2385,19 @@
       <c r="A69" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2685,19 +2685,19 @@
       <c r="A81" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2785,19 +2785,19 @@
       <c r="A85" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3342,129 +3342,154 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="A110" s="4" t="inlineStr">
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr"/>
-      <c r="E110" s="4" t="inlineStr"/>
-    </row>
-    <row r="111" ht="26" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="D111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B111" s="6" t="n">
+      <c r="B112" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C111" s="7" t="inlineStr">
+      <c r="C112" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="inlineStr"/>
-      <c r="E111" s="7" t="inlineStr"/>
-    </row>
-    <row r="112" ht="26" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="C112" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr"/>
       <c r="E112" s="7" t="inlineStr"/>
     </row>
     <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr"/>
     </row>
     <row r="114" ht="26" customHeight="1">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B114" s="6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr"/>
     </row>
     <row r="115" ht="26" customHeight="1">
-      <c r="A115" s="12" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr"/>
+      <c r="E115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116" ht="26" customHeight="1">
+      <c r="A116" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B115" s="13" t="n">
-        <v>103</v>
-      </c>
-      <c r="C115" s="14" t="inlineStr"/>
-      <c r="D115" s="14" t="inlineStr"/>
-      <c r="E115" s="14" t="inlineStr"/>
-    </row>
-    <row r="117" ht="76" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
+      <c r="B116" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="C116" s="14" t="inlineStr"/>
+      <c r="D116" s="14" t="inlineStr"/>
+      <c r="E116" s="14" t="inlineStr"/>
+    </row>
+    <row r="118" ht="76" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3474,8 +3499,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A110:E110"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費を新たに算定した。決着していない事項は過年度の数値を据え置き、何をどう置いたかを20件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項4件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。諮る資料であり計画素案には入れていない。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案を推している。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,19 +3285,19 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3367,129 +3367,154 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr"/>
-      <c r="E111" s="4" t="inlineStr"/>
-    </row>
-    <row r="112" ht="26" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="D112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B112" s="6" t="n">
+      <c r="B113" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="inlineStr"/>
-      <c r="E112" s="7" t="inlineStr"/>
-    </row>
-    <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr"/>
     </row>
     <row r="114" ht="26" customHeight="1">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B114" s="6" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr"/>
     </row>
     <row r="115" ht="26" customHeight="1">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr"/>
       <c r="E115" s="7" t="inlineStr"/>
     </row>
     <row r="116" ht="26" customHeight="1">
-      <c r="A116" s="12" t="inlineStr">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr"/>
+      <c r="E116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117" ht="26" customHeight="1">
+      <c r="A117" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B116" s="13" t="n">
-        <v>104</v>
-      </c>
-      <c r="C116" s="14" t="inlineStr"/>
-      <c r="D116" s="14" t="inlineStr"/>
-      <c r="E116" s="14" t="inlineStr"/>
-    </row>
-    <row r="118" ht="76" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
+      <c r="B117" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="C117" s="14" t="inlineStr"/>
+      <c r="D117" s="14" t="inlineStr"/>
+      <c r="E117" s="14" t="inlineStr"/>
+    </row>
+    <row r="119" ht="76" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3499,8 +3524,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A111:E111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。諮る資料であり計画素案には入れていない。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案を推している。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
+          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1510,19 +1510,19 @@
       <c r="A34" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
+          <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1585,19 +1585,19 @@
       <c r="A37" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
+          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
+          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1660,19 +1660,19 @@
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1710,19 +1710,19 @@
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1835,19 +1835,19 @@
       <c r="A47" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1910,19 +1910,19 @@
       <c r="A50" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1960,19 +1960,19 @@
       <c r="A52" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1985,19 +1985,19 @@
       <c r="A53" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2010,19 +2010,19 @@
       <c r="A54" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2035,19 +2035,19 @@
       <c r="A55" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2160,19 +2160,19 @@
       <c r="A60" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2210,19 +2210,19 @@
       <c r="A62" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2335,19 +2335,19 @@
       <c r="A67" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2360,19 +2360,19 @@
       <c r="A68" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2660,19 +2660,19 @@
       <c r="A80" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2710,19 +2710,19 @@
       <c r="A82" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2785,19 +2785,19 @@
       <c r="A85" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,136 +3385,261 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>資料提供のご依頼</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_追加調査報告書.xlsx</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>追加で実施した調査の報告</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr"/>
-      <c r="E112" s="4" t="inlineStr"/>
-    </row>
-    <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118" ht="26" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n">
+      <c r="B118" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="7" t="inlineStr"/>
-    </row>
-    <row r="114" ht="26" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr"/>
+      <c r="E118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119" ht="26" customHeight="1">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr"/>
-      <c r="E114" s="7" t="inlineStr"/>
-    </row>
-    <row r="115" ht="26" customHeight="1">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr"/>
+      <c r="E119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120" ht="26" customHeight="1">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="B115" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="B120" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr"/>
-      <c r="E115" s="7" t="inlineStr"/>
-    </row>
-    <row r="116" ht="26" customHeight="1">
-      <c r="A116" s="10" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr"/>
+      <c r="E120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121" ht="26" customHeight="1">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="B116" s="6" t="n">
+      <c r="B121" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C116" s="7" t="inlineStr">
+      <c r="C121" s="7" t="inlineStr">
         <is>
           <t>本業務の成果品ではない</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr"/>
-      <c r="E116" s="7" t="inlineStr"/>
-    </row>
-    <row r="117" ht="26" customHeight="1">
-      <c r="A117" s="12" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr"/>
+      <c r="E121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122" ht="26" customHeight="1">
+      <c r="A122" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B117" s="13" t="n">
-        <v>105</v>
-      </c>
-      <c r="C117" s="14" t="inlineStr"/>
-      <c r="D117" s="14" t="inlineStr"/>
-      <c r="E117" s="14" t="inlineStr"/>
-    </row>
-    <row r="119" ht="76" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
+      <c r="B122" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="C122" s="14" t="inlineStr"/>
+      <c r="D122" s="14" t="inlineStr"/>
+      <c r="E122" s="14" t="inlineStr"/>
+    </row>
+    <row r="124" ht="76" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3524,8 +3649,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A119:E119"/>
-    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A124:E124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3410,19 +3410,19 @@
       <c r="A110" s="6" t="n">
         <v>106</v>
       </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,129 +3517,154 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="28" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr"/>
-      <c r="E117" s="4" t="inlineStr"/>
-    </row>
-    <row r="118" ht="26" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119" ht="26" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B118" s="6" t="n">
+      <c r="B119" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr"/>
-      <c r="E118" s="7" t="inlineStr"/>
-    </row>
-    <row r="119" ht="26" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr"/>
       <c r="E119" s="7" t="inlineStr"/>
     </row>
     <row r="120" ht="26" customHeight="1">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B120" s="6" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr"/>
       <c r="E120" s="7" t="inlineStr"/>
     </row>
     <row r="121" ht="26" customHeight="1">
-      <c r="A121" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr"/>
       <c r="E121" s="7" t="inlineStr"/>
     </row>
     <row r="122" ht="26" customHeight="1">
-      <c r="A122" s="12" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr"/>
+      <c r="E122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123" ht="26" customHeight="1">
+      <c r="A123" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B122" s="13" t="n">
-        <v>110</v>
-      </c>
-      <c r="C122" s="14" t="inlineStr"/>
-      <c r="D122" s="14" t="inlineStr"/>
-      <c r="E122" s="14" t="inlineStr"/>
-    </row>
-    <row r="124" ht="76" customHeight="1">
-      <c r="A124" s="11" t="inlineStr">
+      <c r="B123" s="13" t="n">
+        <v>111</v>
+      </c>
+      <c r="C123" s="14" t="inlineStr"/>
+      <c r="D123" s="14" t="inlineStr"/>
+      <c r="E123" s="14" t="inlineStr"/>
+    </row>
+    <row r="125" ht="76" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3649,8 +3674,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A125:E125"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3410,19 +3410,19 @@
       <c r="A110" s="6" t="n">
         <v>106</v>
       </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3510,19 +3510,19 @@
       <c r="A114" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,129 +3542,154 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D116" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="28" customHeight="1">
-      <c r="A118" s="4" t="inlineStr">
+    <row r="119" ht="28" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr"/>
-      <c r="E118" s="4" t="inlineStr"/>
-    </row>
-    <row r="119" ht="26" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120" ht="26" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B119" s="6" t="n">
+      <c r="B120" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr"/>
-      <c r="E119" s="7" t="inlineStr"/>
-    </row>
-    <row r="120" ht="26" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr"/>
       <c r="E120" s="7" t="inlineStr"/>
     </row>
     <row r="121" ht="26" customHeight="1">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr"/>
       <c r="E121" s="7" t="inlineStr"/>
     </row>
     <row r="122" ht="26" customHeight="1">
-      <c r="A122" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr"/>
       <c r="E122" s="7" t="inlineStr"/>
     </row>
     <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="12" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr"/>
+      <c r="E123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124" ht="26" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B123" s="13" t="n">
-        <v>111</v>
-      </c>
-      <c r="C123" s="14" t="inlineStr"/>
-      <c r="D123" s="14" t="inlineStr"/>
-      <c r="E123" s="14" t="inlineStr"/>
-    </row>
-    <row r="125" ht="76" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
+      <c r="B124" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="C124" s="14" t="inlineStr"/>
+      <c r="D124" s="14" t="inlineStr"/>
+      <c r="E124" s="14" t="inlineStr"/>
+    </row>
+    <row r="126" ht="76" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3674,8 +3699,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A117:E117"/>
-    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A126:E126"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2517,12 +2517,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2660,19 +2660,19 @@
       <c r="A80" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2685,19 +2685,19 @@
       <c r="A81" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3535,19 +3535,19 @@
       <c r="A115" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3567,129 +3567,154 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
+      <c r="D117" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="28" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr"/>
-      <c r="E119" s="4" t="inlineStr"/>
-    </row>
-    <row r="120" ht="26" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121" ht="26" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B120" s="6" t="n">
+      <c r="B121" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="C121" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="inlineStr"/>
-      <c r="E120" s="7" t="inlineStr"/>
-    </row>
-    <row r="121" ht="26" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr"/>
       <c r="E121" s="7" t="inlineStr"/>
     </row>
     <row r="122" ht="26" customHeight="1">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B122" s="6" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr"/>
       <c r="E122" s="7" t="inlineStr"/>
     </row>
     <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr"/>
       <c r="E123" s="7" t="inlineStr"/>
     </row>
     <row r="124" ht="26" customHeight="1">
-      <c r="A124" s="12" t="inlineStr">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr"/>
+      <c r="E124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125" ht="26" customHeight="1">
+      <c r="A125" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B124" s="13" t="n">
-        <v>112</v>
-      </c>
-      <c r="C124" s="14" t="inlineStr"/>
-      <c r="D124" s="14" t="inlineStr"/>
-      <c r="E124" s="14" t="inlineStr"/>
-    </row>
-    <row r="126" ht="76" customHeight="1">
-      <c r="A126" s="11" t="inlineStr">
+      <c r="B125" s="13" t="n">
+        <v>113</v>
+      </c>
+      <c r="C125" s="14" t="inlineStr"/>
+      <c r="D125" s="14" t="inlineStr"/>
+      <c r="E125" s="14" t="inlineStr"/>
+    </row>
+    <row r="127" ht="76" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3699,8 +3724,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A127:E127"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1110,19 +1110,19 @@
       <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_アンケート分析_点検箇所と手順.docx</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>4調査の集計。限界と留保を各シートに明記している</t>
+          <t>アンケート調査の分析について、この業務に携わっていない者が点検するための資料（全10節）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。成果品のシート数・段落数は実物を開いて数え、自己点検の件数はソースの呼出しを数え、留保・所見は集計分析報告書の実物から読んでいる。特に見る箇所として、母集団の書き方、在籍と受給の書き分け、率と実数の併記、見込量のじか書き、反映済みの判定、留保の落とし、個票の非収録を挙げた。この作業で実際に起きた誤り7件を、気づいた経緯と手立てとともに掲げた。個人情報は値の形（正規表現）で、禁止表現は語で探す方法を示している。点検の記録様式と分担の案を含む</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1135,19 +1135,19 @@
       <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
+          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>進行者の手元資料。会議運営上の想定を含む</t>
+          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案 第2章第4節への反映、調査結果と保険者の実績（年報 令和7年度）の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保をまとめている。9月に新たにできるようになったのは、年報の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違う。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠はいずれも成果品の実物から読んでおり、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1160,19 +1160,19 @@
       <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>進行者の手元資料。想定問答と着地点を含む</t>
+          <t>4調査の集計。限界と留保を各シートに明記している</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1185,19 +1185,19 @@
       <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>進行者の手元資料。会議運営上の想定を含む</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1210,19 +1210,19 @@
       <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>進行者の手元資料。想定問答と着地点を含む</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1235,19 +1235,19 @@
       <c r="A23" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>更新版の作成過程の版。配布は更新版による</t>
+          <t>受託者による校正の記録</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1310,19 +1310,19 @@
       <c r="A26" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>受託者による会議資料の自己点検の記録</t>
+          <t>更新版の作成過程の版。配布は更新版による</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1360,19 +1360,19 @@
       <c r="A28" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>受託者による校正の記録</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1385,19 +1385,19 @@
       <c r="A29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>受託者による会議資料の自己点検の記録</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1435,19 +1435,19 @@
       <c r="A31" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
+          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1485,19 +1485,19 @@
       <c r="A33" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1510,19 +1510,19 @@
       <c r="A34" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
+          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1535,19 +1535,19 @@
       <c r="A35" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1560,19 +1560,19 @@
       <c r="A36" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
+          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1610,19 +1610,19 @@
       <c r="A38" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
+          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1635,19 +1635,19 @@
       <c r="A39" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
+          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1685,19 +1685,19 @@
       <c r="A41" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1710,19 +1710,19 @@
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない</t>
+          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1735,19 +1735,19 @@
       <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1760,19 +1760,19 @@
       <c r="A44" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1860,19 +1860,19 @@
       <c r="A48" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1885,19 +1885,19 @@
       <c r="A49" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1935,19 +1935,19 @@
       <c r="A51" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1960,19 +1960,19 @@
       <c r="A52" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1985,19 +1985,19 @@
       <c r="A53" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2035,19 +2035,19 @@
       <c r="A55" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2085,19 +2085,19 @@
       <c r="A57" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2185,19 +2185,19 @@
       <c r="A61" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2210,19 +2210,19 @@
       <c r="A62" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2235,19 +2235,19 @@
       <c r="A63" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2260,19 +2260,19 @@
       <c r="A64" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2360,19 +2360,19 @@
       <c r="A68" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2660,19 +2660,19 @@
       <c r="A80" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2785,19 +2785,19 @@
       <c r="A85" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2810,19 +2810,19 @@
       <c r="A86" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3535,19 +3535,19 @@
       <c r="A115" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,136 +3585,186 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="9" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="28" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr"/>
-      <c r="E120" s="4" t="inlineStr"/>
-    </row>
-    <row r="121" ht="26" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123" ht="26" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B121" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="B123" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr"/>
-      <c r="E121" s="7" t="inlineStr"/>
-    </row>
-    <row r="122" ht="26" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="C122" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="inlineStr"/>
-      <c r="E122" s="7" t="inlineStr"/>
-    </row>
-    <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr"/>
       <c r="E123" s="7" t="inlineStr"/>
     </row>
     <row r="124" ht="26" customHeight="1">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B124" s="6" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr"/>
       <c r="E124" s="7" t="inlineStr"/>
     </row>
     <row r="125" ht="26" customHeight="1">
-      <c r="A125" s="12" t="inlineStr">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>納品時又は求めに応じて提出する</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr"/>
+      <c r="E125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126" ht="26" customHeight="1">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr"/>
+      <c r="E126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127" ht="26" customHeight="1">
+      <c r="A127" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B125" s="13" t="n">
-        <v>113</v>
-      </c>
-      <c r="C125" s="14" t="inlineStr"/>
-      <c r="D125" s="14" t="inlineStr"/>
-      <c r="E125" s="14" t="inlineStr"/>
-    </row>
-    <row r="127" ht="76" customHeight="1">
-      <c r="A127" s="11" t="inlineStr">
+      <c r="B127" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="C127" s="14" t="inlineStr"/>
+      <c r="D127" s="14" t="inlineStr"/>
+      <c r="E127" s="14" t="inlineStr"/>
+    </row>
+    <row r="129" ht="76" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3724,8 +3774,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A119:E119"/>
-    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A129:E129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,19 +3285,19 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。令和7年度のみ129,580,267円（4.20％）の差があり、令和6年度・令和8年度は円単位で一致する。差は3町とも同じ向きに出ており、前年度からの伸びは広域連合のファイルだけが趨勢から外れている。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3510,19 +3510,19 @@
       <c r="A114" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3535,19 +3535,19 @@
       <c r="A115" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3610,19 +3610,19 @@
       <c r="A118" s="6" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3642,129 +3642,154 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="28" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr"/>
-      <c r="E122" s="4" t="inlineStr"/>
-    </row>
-    <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124" ht="26" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B123" s="6" t="n">
+      <c r="B124" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="C123" s="7" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D123" s="7" t="inlineStr"/>
-      <c r="E123" s="7" t="inlineStr"/>
-    </row>
-    <row r="124" ht="26" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr"/>
       <c r="E124" s="7" t="inlineStr"/>
     </row>
     <row r="125" ht="26" customHeight="1">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr"/>
       <c r="E125" s="7" t="inlineStr"/>
     </row>
     <row r="126" ht="26" customHeight="1">
-      <c r="A126" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B126" s="6" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr"/>
       <c r="E126" s="7" t="inlineStr"/>
     </row>
     <row r="127" ht="26" customHeight="1">
-      <c r="A127" s="12" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr"/>
+      <c r="E127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128" ht="26" customHeight="1">
+      <c r="A128" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B127" s="13" t="n">
-        <v>115</v>
-      </c>
-      <c r="C127" s="14" t="inlineStr"/>
-      <c r="D127" s="14" t="inlineStr"/>
-      <c r="E127" s="14" t="inlineStr"/>
-    </row>
-    <row r="129" ht="76" customHeight="1">
-      <c r="A129" s="11" t="inlineStr">
+      <c r="B128" s="13" t="n">
+        <v>116</v>
+      </c>
+      <c r="C128" s="14" t="inlineStr"/>
+      <c r="D128" s="14" t="inlineStr"/>
+      <c r="E128" s="14" t="inlineStr"/>
+    </row>
+    <row r="130" ht="76" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3774,8 +3799,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A130:E130"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2085,19 +2085,19 @@
       <c r="A57" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2110,19 +2110,19 @@
       <c r="A58" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2235,19 +2235,19 @@
       <c r="A63" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2285,19 +2285,19 @@
       <c r="A65" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2660,19 +2660,19 @@
       <c r="A80" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2710,19 +2710,19 @@
       <c r="A82" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2810,19 +2810,19 @@
       <c r="A86" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,19 +3285,19 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3535,19 +3535,19 @@
       <c r="A115" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,19 +3585,19 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3635,19 +3635,19 @@
       <c r="A119" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3667,129 +3667,154 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D120" s="7" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="28" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr"/>
-      <c r="E123" s="4" t="inlineStr"/>
-    </row>
-    <row r="124" ht="26" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125" ht="26" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B124" s="6" t="n">
+      <c r="B125" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="C124" s="7" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="inlineStr"/>
-      <c r="E124" s="7" t="inlineStr"/>
-    </row>
-    <row r="125" ht="26" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="C125" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr"/>
       <c r="E125" s="7" t="inlineStr"/>
     </row>
     <row r="126" ht="26" customHeight="1">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B126" s="6" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr"/>
       <c r="E126" s="7" t="inlineStr"/>
     </row>
     <row r="127" ht="26" customHeight="1">
-      <c r="A127" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr"/>
       <c r="E127" s="7" t="inlineStr"/>
     </row>
     <row r="128" ht="26" customHeight="1">
-      <c r="A128" s="12" t="inlineStr">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr"/>
+      <c r="E128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129" ht="26" customHeight="1">
+      <c r="A129" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B128" s="13" t="n">
-        <v>116</v>
-      </c>
-      <c r="C128" s="14" t="inlineStr"/>
-      <c r="D128" s="14" t="inlineStr"/>
-      <c r="E128" s="14" t="inlineStr"/>
-    </row>
-    <row r="130" ht="76" customHeight="1">
-      <c r="A130" s="11" t="inlineStr">
+      <c r="B129" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="C129" s="14" t="inlineStr"/>
+      <c r="D129" s="14" t="inlineStr"/>
+      <c r="E129" s="14" t="inlineStr"/>
+    </row>
+    <row r="131" ht="76" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3799,8 +3824,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A123:E123"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>令和8年10月工程の「地域課題整理資料」と「3町協議資料」。地域課題15件を根拠となる数値・出所・計画本文の反映先と対にして掲げ、町ごとの確認事項（東川町・美瑛町・東神楽町）と3町共通の確認事項を業務工程管理表から読んで一覧にした。認知症基本法第13条の市町村認知症施策推進計画（案B）について、保険者機能強化推進交付金等の認知症総合支援の町別評価を踏まえ、各町で決めていただく事項を掲げている。全ての確認事項に「決まらない場合の当方の扱い」を置いている</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1035,19 +1035,19 @@
       <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1085,19 +1085,19 @@
       <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1110,19 +1110,19 @@
       <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート分析_点検箇所と手順.docx</t>
+          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>アンケート調査の分析について、この業務に携わっていない者が点検するための資料（全10節）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。成果品のシート数・段落数は実物を開いて数え、自己点検の件数はソースの呼出しを数え、留保・所見は集計分析報告書の実物から読んでいる。特に見る箇所として、母集団の書き方、在籍と受給の書き分け、率と実数の併記、見込量のじか書き、反映済みの判定、留保の落とし、個票の非収録を挙げた。この作業で実際に起きた誤り7件を、気づいた経緯と手立てとともに掲げた。個人情報は値の形（正規表現）で、禁止表現は語で探す方法を示している。点検の記録様式と分担の案を含む</t>
+          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1135,19 +1135,19 @@
       <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
+          <t>第10期計画_アンケート分析_点検箇所と手順.docx</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案 第2章第4節への反映、調査結果と保険者の実績（年報 令和7年度）の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保をまとめている。9月に新たにできるようになったのは、年報の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違う。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠はいずれも成果品の実物から読んでおり、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。ご判断をお願いする事項3件を含む</t>
+          <t>アンケート調査の分析について、この業務に携わっていない者が点検するための資料（全10節）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。成果品のシート数・段落数は実物を開いて数え、自己点検の件数はソースの呼出しを数え、留保・所見は集計分析報告書の実物から読んでいる。特に見る箇所として、母集団の書き方、在籍と受給の書き分け、率と実数の併記、見込量のじか書き、反映済みの判定、留保の落とし、個票の非収録を挙げた。この作業で実際に起きた誤り7件を、気づいた経緯と手立てとともに掲げた。個人情報は値の形（正規表現）で、禁止表現は語で探す方法を示している。点検の記録様式と分担の案を含む</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>4調査の集計。限界と留保を各シートに明記している</t>
+          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案 第2章第4節への反映、調査結果と保険者の実績（年報 令和7年度）の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保をまとめている。9月に新たにできるようになったのは、年報の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違う。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠はいずれも成果品の実物から読んでおり、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1185,19 +1185,19 @@
       <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>進行者の手元資料。会議運営上の想定を含む</t>
+          <t>4調査の集計。限界と留保を各シートに明記している</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
+          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>進行者の手元資料。想定問答と着地点を含む</t>
+          <t>進行者の手元資料。会議運営上の想定を含む</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1235,19 +1235,19 @@
       <c r="A23" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>進行者の手元資料。想定問答と着地点を含む</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1285,19 +1285,19 @@
       <c r="A25" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1310,19 +1310,19 @@
       <c r="A26" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
+          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
+          <t>受託者による校正の記録</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1335,19 +1335,19 @@
       <c r="A27" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>更新版の作成過程の版。配布は更新版による</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録</t>
+          <t>更新版の作成過程の版。配布は更新版による</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>受託者による会議資料の自己点検の記録</t>
+          <t>受託者による校正の記録</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1410,19 +1410,19 @@
       <c r="A30" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>受託者による会議資料の自己点検の記録</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1435,19 +1435,19 @@
       <c r="A31" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1460,19 +1460,19 @@
       <c r="A32" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
+          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
+          <t>いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1535,19 +1535,19 @@
       <c r="A35" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
+          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
+          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1585,19 +1585,19 @@
       <c r="A37" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
+          <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1660,19 +1660,19 @@
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
+          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
+          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1735,19 +1735,19 @@
       <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1785,19 +1785,19 @@
       <c r="A45" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1910,19 +1910,19 @@
       <c r="A50" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1985,19 +1985,19 @@
       <c r="A53" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2035,19 +2035,19 @@
       <c r="A55" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2060,19 +2060,19 @@
       <c r="A56" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2110,19 +2110,19 @@
       <c r="A58" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2260,19 +2260,19 @@
       <c r="A64" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2310,19 +2310,19 @@
       <c r="A66" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2685,19 +2685,19 @@
       <c r="A81" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2785,19 +2785,19 @@
       <c r="A85" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,19 +3285,19 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3510,19 +3510,19 @@
       <c r="A114" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,19 +3585,19 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3610,19 +3610,19 @@
       <c r="A118" s="6" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3692,129 +3692,154 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr"/>
-      <c r="E124" s="4" t="inlineStr"/>
-    </row>
-    <row r="125" ht="26" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126" ht="26" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B125" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="B126" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D125" s="7" t="inlineStr"/>
-      <c r="E125" s="7" t="inlineStr"/>
-    </row>
-    <row r="126" ht="26" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr"/>
       <c r="E126" s="7" t="inlineStr"/>
     </row>
     <row r="127" ht="26" customHeight="1">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr"/>
       <c r="E127" s="7" t="inlineStr"/>
     </row>
     <row r="128" ht="26" customHeight="1">
-      <c r="A128" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B128" s="6" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr"/>
       <c r="E128" s="7" t="inlineStr"/>
     </row>
     <row r="129" ht="26" customHeight="1">
-      <c r="A129" s="12" t="inlineStr">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr"/>
+      <c r="E129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130" ht="26" customHeight="1">
+      <c r="A130" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B129" s="13" t="n">
-        <v>117</v>
-      </c>
-      <c r="C129" s="14" t="inlineStr"/>
-      <c r="D129" s="14" t="inlineStr"/>
-      <c r="E129" s="14" t="inlineStr"/>
-    </row>
-    <row r="131" ht="76" customHeight="1">
-      <c r="A131" s="11" t="inlineStr">
+      <c r="B130" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="C130" s="14" t="inlineStr"/>
+      <c r="D130" s="14" t="inlineStr"/>
+      <c r="E130" s="14" t="inlineStr"/>
+    </row>
+    <row r="132" ht="76" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3824,8 +3849,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A131:E131"/>
-    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A124:E124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
+          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1810,19 +1810,19 @@
       <c r="A46" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1835,19 +1835,19 @@
       <c r="A47" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1935,19 +1935,19 @@
       <c r="A51" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1960,19 +1960,19 @@
       <c r="A52" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2010,19 +2010,19 @@
       <c r="A54" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2035,19 +2035,19 @@
       <c r="A55" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2060,19 +2060,19 @@
       <c r="A56" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2110,19 +2110,19 @@
       <c r="A58" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2185,19 +2185,19 @@
       <c r="A61" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2285,19 +2285,19 @@
       <c r="A65" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2310,19 +2310,19 @@
       <c r="A66" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2335,19 +2335,19 @@
       <c r="A67" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2360,19 +2360,19 @@
       <c r="A68" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2660,19 +2660,19 @@
       <c r="A80" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2685,19 +2685,19 @@
       <c r="A81" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2710,19 +2710,19 @@
       <c r="A82" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2885,19 +2885,19 @@
       <c r="A89" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3510,19 +3510,19 @@
       <c r="A114" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,19 +3585,19 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3685,19 +3685,19 @@
       <c r="A121" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,136 +3710,186 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="9" t="inlineStr">
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr"/>
-      <c r="E125" s="4" t="inlineStr"/>
-    </row>
-    <row r="126" ht="26" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128" ht="26" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B126" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
+      <c r="B128" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr"/>
-      <c r="E126" s="7" t="inlineStr"/>
-    </row>
-    <row r="127" ht="26" customHeight="1">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr"/>
-      <c r="E127" s="7" t="inlineStr"/>
-    </row>
-    <row r="128" ht="26" customHeight="1">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr"/>
       <c r="E128" s="7" t="inlineStr"/>
     </row>
     <row r="129" ht="26" customHeight="1">
-      <c r="A129" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr"/>
       <c r="E129" s="7" t="inlineStr"/>
     </row>
     <row r="130" ht="26" customHeight="1">
-      <c r="A130" s="12" t="inlineStr">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>納品時又は求めに応じて提出する</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr"/>
+      <c r="E130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131" ht="26" customHeight="1">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr"/>
+      <c r="E131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132" ht="26" customHeight="1">
+      <c r="A132" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B130" s="13" t="n">
-        <v>118</v>
-      </c>
-      <c r="C130" s="14" t="inlineStr"/>
-      <c r="D130" s="14" t="inlineStr"/>
-      <c r="E130" s="14" t="inlineStr"/>
-    </row>
-    <row r="132" ht="76" customHeight="1">
-      <c r="A132" s="11" t="inlineStr">
+      <c r="B132" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="C132" s="14" t="inlineStr"/>
+      <c r="D132" s="14" t="inlineStr"/>
+      <c r="E132" s="14" t="inlineStr"/>
+    </row>
+    <row r="134" ht="76" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3849,8 +3899,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A132:E132"/>
-    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A126:E126"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -960,19 +960,19 @@
       <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx</t>
+          <t>第10期介護保険事業計画_公表版.docx</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>［要協議］ほか未確定事項を本文に残している。協議用であることを表紙に明示している</t>
+          <t>計画をお読みになる方（住民・策定委員会の委員）に向けた版。協議用素案から組み替えたものであり、本文・数値を別に持たない（協議用素案を改めれば本版も追随する）。打合せでご判断いただくための分析15件を落とし、介護サービスの内容29区分と用語の解説29語を巻末に加えている。章の見出しに帯を付け、表の見出し行を各ページで繰り返す。未確定箇所が残る間は表紙に「公表版（体裁確認用）」と記し、すべて解消した時点で「公表版」となる</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_骨子案.docx</t>
+          <t>第10期介護保険事業計画_協議用素案_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>章立てと根拠資料の対照。決定・確認を要する事項12件を含む</t>
+          <t>［要協議］ほか未確定事項を本文に残している。協議用であることを表紙に明示している</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1010,19 +1010,19 @@
       <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx</t>
+          <t>第10期介護保険事業計画_骨子案.docx</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月工程の「地域課題整理資料」と「3町協議資料」。地域課題15件を根拠となる数値・出所・計画本文の反映先と対にして掲げ、町ごとの確認事項（東川町・美瑛町・東神楽町）と3町共通の確認事項を業務工程管理表から読んで一覧にした。認知症基本法第13条の市町村認知症施策推進計画（案B）について、保険者機能強化推進交付金等の認知症総合支援の町別評価を踏まえ、各町で決めていただく事項を掲げている。全ての確認事項に「決まらない場合の当方の扱い」を置いている</t>
+          <t>章立てと根拠資料の対照。決定・確認を要する事項12件を含む</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>令和8年10月工程の「地域課題整理資料」と「3町協議資料」。地域課題15件を根拠となる数値・出所・計画本文の反映先と対にして掲げ、町ごとの確認事項（東川町・美瑛町・東神楽町）と3町共通の確認事項を業務工程管理表から読んで一覧にした。認知症基本法第13条の市町村認知症施策推進計画（案B）について、保険者機能強化推進交付金等の認知症総合支援の町別評価を踏まえ、各町で決めていただく事項を掲げている。全ての確認事項に「決まらない場合の当方の扱い」を置いている</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1060,19 +1060,19 @@
       <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1110,19 +1110,19 @@
       <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1135,19 +1135,19 @@
       <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート分析_点検箇所と手順.docx</t>
+          <t>第10期計画_3町合同意見交換会資料.docx</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>アンケート調査の分析について、この業務に携わっていない者が点検するための資料（全10節）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。成果品のシート数・段落数は実物を開いて数え、自己点検の件数はソースの呼出しを数え、留保・所見は集計分析報告書の実物から読んでいる。特に見る箇所として、母集団の書き方、在籍と受給の書き分け、率と実数の併記、見込量のじか書き、反映済みの判定、留保の落とし、個票の非収録を挙げた。この作業で実際に起きた誤り7件を、気づいた経緯と手立てとともに掲げた。個人情報は値の形（正規表現）で、禁止表現は語で探す方法を示している。点検の記録様式と分担の案を含む</t>
+          <t>令和8年10月上旬の構成3町合同の意見交換会で用いる資料。第10期計画の策定の状況、サービス見込量・給付費・保険料の試算（第1次概算）、保険料の月額を動かす前提、地域課題15件、3町共通の確認事項、認知症施策推進計画の扱い、資料のご提供のお願い及び10月以降の工程を1冊にまとめたもの。ご決定をお願いする事項には、すべて「決まらない場合の当方の扱い」（受託者の仮置き）を置いており、うち計画素案へ反映した6件は反映した内容を併せて掲げている。町ごとの個別協議の確認事項は「10月 地域課題の整理と3町協議の確認事項」による</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
+          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案 第2章第4節への反映、調査結果と保険者の実績（年報 令和7年度）の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保をまとめている。9月に新たにできるようになったのは、年報の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違う。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠はいずれも成果品の実物から読んでおり、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。ご判断をお願いする事項3件を含む</t>
+          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1185,19 +1185,19 @@
       <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_アンケート分析_点検箇所と手順.docx</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>4調査の集計。限界と留保を各シートに明記している</t>
+          <t>アンケート調査の分析について、この業務に携わっていない者が点検するための資料（全10節）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。成果品のシート数・段落数は実物を開いて数え、自己点検の件数はソースの呼出しを数え、留保・所見は集計分析報告書によっている。特に見る箇所として、母集団の書き方、在籍と受給の書き分け、率と実数の併記、見込量のじか書き、反映済みの判定、留保の落とし、個票の非収録を挙げた。この作業で実際に起きた誤り7件を、気づいた経緯と手立てとともに掲げた。個人情報は値の形（正規表現）で、禁止表現は語で探す方法を示している。点検の記録様式と分担の案を含む</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1210,19 +1210,19 @@
       <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
+          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>進行者の手元資料。会議運営上の想定を含む</t>
+          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案 第2章第4節への反映、調査結果と保険者の実績（年報 令和7年度）の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保をまとめている。9月に新たにできるようになったのは、年報の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違う。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠はいずれも成果品によっており、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1235,19 +1235,19 @@
       <c r="A23" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>進行者の手元資料。想定問答と着地点を含む</t>
+          <t>4調査の集計。限界と留保を各シートに明記している</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1260,19 +1260,19 @@
       <c r="A24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>進行者の手元資料。会議運営上の想定を含む</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1285,19 +1285,19 @@
       <c r="A25" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>進行者の手元資料。想定問答と着地点を含む</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1310,19 +1310,19 @@
       <c r="A26" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>更新版の作成過程の版。配布は更新版による</t>
+          <t>受託者による校正の記録</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1385,19 +1385,19 @@
       <c r="A29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>受託者による会議資料の自己点検の記録</t>
+          <t>更新版の作成過程の版。配布は更新版による</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1435,19 +1435,19 @@
       <c r="A31" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>受託者による校正の記録</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1460,19 +1460,19 @@
       <c r="A32" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>受託者による会議資料の自己点検の記録</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1510,19 +1510,19 @@
       <c r="A34" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_サービス見込量の算定.xlsx</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
+          <t>サービス見込量・給付費・保険料の算定（全18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項を収めている。見込量を掲げるほかの成果品と計画素案 第6章はいずれも本算定による。工程ごとに提示する版は別に残している（第1次概算＝令和8年9月26日、第2次概算＝令和8年10月30日）。決着していない事項は過年度の数値を据え置き、何をどう置いたかを据え置きの一覧に掲げている</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1560,19 +1560,19 @@
       <c r="A36" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
+          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1585,19 +1585,19 @@
       <c r="A37" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
+          <t>令和8年9月26日に提示した第1次概算の版。提示した時点の値を残すため、以後は作り直していない（算定を改めた後の値は「第10期計画_サービス見込量の算定.xlsx」による）。いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1610,19 +1610,19 @@
       <c r="A38" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第2次概算.xlsx</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>第2次概算（令和8年10月30日）の組立て。第1次概算（令和8年9月26日）からの差分、保険料算定表の記号A〜Jの対照、見込量・利用回（日）数・給付費の種別ごとの差分、中長期推計、月額を動かす前提、見える化システムの出力との対照、残る未決と既定値、10月30日までに行うことを掲げている。算定そのものは「第10期計画_サービス見込量の算定.xlsx」による。既定値（決着しない場合の扱い）によって算定しているため、ご決定をいただいた事項は10月30日の再算定で置き換わる</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1635,19 +1635,19 @@
       <c r="A39" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
+          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1660,19 +1660,19 @@
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
+          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1710,19 +1710,19 @@
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
+          <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1735,19 +1735,19 @@
       <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
+          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1785,19 +1785,19 @@
       <c r="A45" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
+          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
+          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1810,19 +1810,19 @@
       <c r="A46" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
+          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1835,19 +1835,19 @@
       <c r="A47" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
+          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1860,19 +1860,19 @@
       <c r="A48" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1885,19 +1885,19 @@
       <c r="A49" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1910,19 +1910,19 @@
       <c r="A50" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1935,19 +1935,19 @@
       <c r="A51" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_交付金評価の取りまとめと第10期への反映.pdf</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>同左のPDF版。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1960,19 +1960,19 @@
       <c r="A52" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_交付金評価の取りまとめと第10期への反映.xlsx</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>交付金の評価結果を推移・全国との比較・未得点項目の3つの側から取りまとめ、第10期計画への反映の可否を判定したもの。3町の得点は3か年ほぼ横ばいである一方、全国平均が32.5点上がったため全国での位置は下がっている。大項目別に改善14件・低下14件を掲げ、全国の多くの市町村が得点しているのに3町とも0点である明細列38件を17の大項目に束ねて、可4・条件付き12・現時点では不可1と判定した。構成3町のうち一部の町のみ得点している明細列78件は区域内で広げる余地がある。全国集計から広域連合・一部事務組合38団体と構成市町村205を割り出し、構成市町村の得点の平均で比べたところ、当連合は38団体中36位・町村のみで構成する11団体中10位・北海道内4団体の中で最も低い。19施策を介して計画素案の章節・10月の協議資料・確認事項と対にしている</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2010,19 +2010,19 @@
       <c r="A54" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2035,19 +2035,19 @@
       <c r="A55" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2110,19 +2110,19 @@
       <c r="A58" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2160,19 +2160,19 @@
       <c r="A60" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件はリポジトリに格納していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2260,19 +2260,19 @@
       <c r="A64" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2335,19 +2335,19 @@
       <c r="A67" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_図表データ管理台帳.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2785,19 +2785,19 @@
       <c r="A85" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2810,19 +2810,19 @@
       <c r="A86" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2885,19 +2885,19 @@
       <c r="A89" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。ビルドスクリプト101本のうち98本は再実行でき、残る3本は受領資料をセッション固有の場所から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用者数は整数、利用回（日）数は小数第1位で、要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は素案の実物から、確認事項は業務工程管理表のソースから数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,031,900,444円、算定上の月額基準額6,436円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,436円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3635,19 +3635,19 @@
       <c r="A119" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3685,19 +3685,19 @@
       <c r="A121" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,19 +3710,19 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3735,19 +3735,19 @@
       <c r="A123" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,136 +3760,461 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="9" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>集計値のみを収録している（個票は収録していない）</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>資料提供のご依頼</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_追加調査報告書.xlsx</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>追加で実施した調査の報告</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
         <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="3" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="28" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
+    <row r="140" ht="28" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr"/>
-      <c r="E127" s="4" t="inlineStr"/>
-    </row>
-    <row r="128" ht="26" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141" ht="26" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B128" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="B141" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr"/>
-      <c r="E128" s="7" t="inlineStr"/>
-    </row>
-    <row r="129" ht="26" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr"/>
+      <c r="E141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142" ht="26" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
         <is>
           <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr"/>
-      <c r="E129" s="7" t="inlineStr"/>
-    </row>
-    <row r="130" ht="26" customHeight="1">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="D142" s="7" t="inlineStr"/>
+      <c r="E142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143" ht="26" customHeight="1">
+      <c r="A143" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="B130" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="B143" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
-      <c r="D130" s="7" t="inlineStr"/>
-      <c r="E130" s="7" t="inlineStr"/>
-    </row>
-    <row r="131" ht="26" customHeight="1">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144" ht="26" customHeight="1">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="B131" s="6" t="n">
+      <c r="B144" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr">
         <is>
           <t>本業務の成果品ではない</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr"/>
-      <c r="E131" s="7" t="inlineStr"/>
-    </row>
-    <row r="132" ht="26" customHeight="1">
-      <c r="A132" s="12" t="inlineStr">
+      <c r="D144" s="7" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145" ht="26" customHeight="1">
+      <c r="A145" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B132" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="C132" s="14" t="inlineStr"/>
-      <c r="D132" s="14" t="inlineStr"/>
-      <c r="E132" s="14" t="inlineStr"/>
-    </row>
-    <row r="134" ht="76" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
+      <c r="B145" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="C145" s="14" t="inlineStr"/>
+      <c r="D145" s="14" t="inlineStr"/>
+      <c r="E145" s="14" t="inlineStr"/>
+    </row>
+    <row r="147" ht="76" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -3899,8 +4224,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A134:E134"/>
-    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A139:E139"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2085,19 +2085,19 @@
       <c r="A57" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_人口推計コーホート分析の妥当性検証.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>社内の人口推計のファイル（令和8年10月1日・10月2日）を点検し、コーホート変化率法の組み方を検証したもの。式の点検7項目のうち3項目が不適合で、東川町だけ90歳以上の変化率の分母が5年前の90歳以上になっている（開放区間であるから5年前の85歳以上を分母とする）。この1点により東川町の総人口が令和32年度で実績の4.7倍へ発散する。95〜99歳・100歳以上に90歳以上の率を流用している点は3町に共通する。正しく組み直すと65歳以上（3町計）は横ばいとなり、当方の案Cと1.4〜4.9％以内で一致する。「令和5年推計を元にした補正」の女は男と全ての欄が同一であり女の値が入っていない。受領資料のスケジュールによりパブリックコメントの期間と令和9年2月以降の会議の日程が分かった（確認事項No.19）。修正の提案11件を優先度の順に掲げている</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2210,19 +2210,19 @@
       <c r="A62" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2260,19 +2260,19 @@
       <c r="A64" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2285,19 +2285,19 @@
       <c r="A65" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2335,19 +2335,19 @@
       <c r="A67" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表データ管理台帳.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2360,19 +2360,19 @@
       <c r="A68" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_図表データ管理台帳.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2385,19 +2385,19 @@
       <c r="A69" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2710,19 +2710,19 @@
       <c r="A82" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2785,19 +2785,19 @@
       <c r="A85" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2810,19 +2810,19 @@
       <c r="A86" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2985,19 +2985,19 @@
       <c r="A93" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,19 +3585,19 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3635,19 +3635,19 @@
       <c r="A119" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3685,19 +3685,19 @@
       <c r="A121" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,19 +3710,19 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3735,19 +3735,19 @@
       <c r="A123" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3810,19 +3810,19 @@
       <c r="A126" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3885,19 +3885,19 @@
       <c r="A129" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3910,19 +3910,19 @@
       <c r="A130" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3960,19 +3960,19 @@
       <c r="A132" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3985,19 +3985,19 @@
       <c r="A133" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4010,19 +4010,19 @@
       <c r="A134" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4060,19 +4060,19 @@
       <c r="A136" s="6" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4092,129 +4092,154 @@
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D137" s="7" t="inlineStr">
+      <c r="D138" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="28" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr"/>
-      <c r="E140" s="4" t="inlineStr"/>
-    </row>
-    <row r="141" ht="26" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+      <c r="D141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142" ht="26" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B141" s="6" t="n">
+      <c r="B142" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="C141" s="7" t="inlineStr">
+      <c r="C142" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D141" s="7" t="inlineStr"/>
-      <c r="E141" s="7" t="inlineStr"/>
-    </row>
-    <row r="142" ht="26" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr"/>
       <c r="E142" s="7" t="inlineStr"/>
     </row>
     <row r="143" ht="26" customHeight="1">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B143" s="6" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr"/>
       <c r="E143" s="7" t="inlineStr"/>
     </row>
     <row r="144" ht="26" customHeight="1">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B144" s="6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr"/>
       <c r="E144" s="7" t="inlineStr"/>
     </row>
     <row r="145" ht="26" customHeight="1">
-      <c r="A145" s="12" t="inlineStr">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr"/>
+      <c r="E145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146" ht="26" customHeight="1">
+      <c r="A146" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B145" s="13" t="n">
-        <v>133</v>
-      </c>
-      <c r="C145" s="14" t="inlineStr"/>
-      <c r="D145" s="14" t="inlineStr"/>
-      <c r="E145" s="14" t="inlineStr"/>
-    </row>
-    <row r="147" ht="76" customHeight="1">
-      <c r="A147" s="11" t="inlineStr">
+      <c r="B146" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="C146" s="14" t="inlineStr"/>
+      <c r="D146" s="14" t="inlineStr"/>
+      <c r="E146" s="14" t="inlineStr"/>
+    </row>
+    <row r="148" ht="76" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4224,8 +4249,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A147:E147"/>
-    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A148:E148"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1685,19 +1685,19 @@
       <c r="A41" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_ヒアリング前事前打合せ_確認事項.xlsx</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
+          <t>令和8年10月8日の事前打合せ（構成3町への町別ヒアリングの前に広域連合と受託者で行うもの）で用いる資料。仮置きによる算定の結果、事前にお決めいただきたい事項（確認先が広域連合であり影響度の点が4点以上のもの）、ヒアリングで構成3町へ伺う事項（町別及び3町共通）と町からご提供をお願いする資料、保険料の月額を動かす前提、ヒアリングの進め方を1枚にまとめたもの。ヒアリングの場で用いる資料は「3町ヒアリング資料」及び「10月 地域課題の整理と3町協議の確認事項」による</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1710,19 +1710,19 @@
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
+          <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1785,19 +1785,19 @@
       <c r="A45" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
+          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
+          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1860,19 +1860,19 @@
       <c r="A48" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
+          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価の取りまとめと第10期への反映.pdf</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>同左のPDF版。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
+          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価の取りまとめと第10期への反映.xlsx</t>
+          <t>第10期計画_交付金評価の取りまとめと第10期への反映.pdf</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>交付金の評価結果を推移・全国との比較・未得点項目の3つの側から取りまとめ、第10期計画への反映の可否を判定したもの。3町の得点は3か年ほぼ横ばいである一方、全国平均が32.5点上がったため全国での位置は下がっている。大項目別に改善14件・低下14件を掲げ、全国の多くの市町村が得点しているのに3町とも0点である明細列38件を17の大項目に束ねて、可4・条件付き12・現時点では不可1と判定した。構成3町のうち一部の町のみ得点している明細列78件は区域内で広げる余地がある。全国集計から広域連合・一部事務組合38団体と構成市町村205を割り出し、構成市町村の得点の平均で比べたところ、当連合は38団体中36位・町村のみで構成する11団体中10位・北海道内4団体の中で最も低い。19施策を介して計画素案の章節・10月の協議資料・確認事項と対にしている</t>
+          <t>同左のPDF版。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_交付金評価の取りまとめと第10期への反映.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
+          <t>交付金の評価結果を推移・全国との比較・未得点項目の3つの側から取りまとめ、第10期計画への反映の可否を判定したもの。3町の得点は3か年ほぼ横ばいである一方、全国平均が32.5点上がったため全国での位置は下がっている。大項目別に改善14件・低下14件を掲げ、全国の多くの市町村が得点しているのに3町とも0点である明細列38件を17の大項目に束ねて、可4・条件付き12・現時点では不可1と判定した。構成3町のうち一部の町のみ得点している明細列78件は区域内で広げる余地がある。全国集計から広域連合・一部事務組合38団体と構成市町村205を割り出し、構成市町村の得点の平均で比べたところ、当連合は38団体中36位・町村のみで構成する11団体中10位・北海道内4団体の中で最も低い。19施策を介して計画素案の章節・10月の協議資料・確認事項と対にしている</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2010,19 +2010,19 @@
       <c r="A54" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2085,19 +2085,19 @@
       <c r="A57" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計コーホート分析の妥当性検証.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>社内の人口推計のファイル（令和8年10月1日・10月2日）を点検し、コーホート変化率法の組み方を検証したもの。式の点検7項目のうち3項目が不適合で、東川町だけ90歳以上の変化率の分母が5年前の90歳以上になっている（開放区間であるから5年前の85歳以上を分母とする）。この1点により東川町の総人口が令和32年度で実績の4.7倍へ発散する。95〜99歳・100歳以上に90歳以上の率を流用している点は3町に共通する。正しく組み直すと65歳以上（3町計）は横ばいとなり、当方の案Cと1.4〜4.9％以内で一致する。「令和5年推計を元にした補正」の女は男と全ての欄が同一であり女の値が入っていない。受領資料のスケジュールによりパブリックコメントの期間と令和9年2月以降の会議の日程が分かった（確認事項No.19）。修正の提案11件を優先度の順に掲げている</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2110,19 +2110,19 @@
       <c r="A58" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_人口推計コーホート分析の妥当性検証.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>社内の人口推計のファイル（令和8年10月1日・10月2日）を点検し、コーホート変化率法の組み方を検証したもの。式の点検7項目のうち3項目が不適合で、東川町だけ90歳以上の変化率の分母が5年前の90歳以上になっている（開放区間であるから5年前の85歳以上を分母とする）。この1点により東川町の総人口が令和32年度で実績の4.7倍へ発散する。95〜99歳・100歳以上に90歳以上の率を流用している点は3町に共通する。正しく組み直すと65歳以上（3町計）は横ばいとなり、当方の案Cと1.4〜4.9％以内で一致する。「令和5年推計を元にした補正」の女は男と全ての欄が同一であり女の値が入っていない。受領資料のスケジュールによりパブリックコメントの期間と令和9年2月以降の会議の日程が分かった（確認事項No.19）。修正の提案11件を優先度の順に掲げている</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2160,19 +2160,19 @@
       <c r="A60" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2235,19 +2235,19 @@
       <c r="A63" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2285,19 +2285,19 @@
       <c r="A65" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2310,19 +2310,19 @@
       <c r="A66" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2360,19 +2360,19 @@
       <c r="A68" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表データ管理台帳.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2385,19 +2385,19 @@
       <c r="A69" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_図表データ管理台帳.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2810,19 +2810,19 @@
       <c r="A86" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2885,19 +2885,19 @@
       <c r="A89" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,19 +3285,19 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3510,19 +3510,19 @@
       <c r="A114" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,19 +3585,19 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3610,19 +3610,19 @@
       <c r="A118" s="6" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3685,19 +3685,19 @@
       <c r="A121" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,19 +3710,19 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3735,19 +3735,19 @@
       <c r="A123" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3810,19 +3810,19 @@
       <c r="A126" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3835,19 +3835,19 @@
       <c r="A127" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3910,19 +3910,19 @@
       <c r="A130" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3935,19 +3935,19 @@
       <c r="A131" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3985,19 +3985,19 @@
       <c r="A133" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4010,19 +4010,19 @@
       <c r="A134" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4035,19 +4035,19 @@
       <c r="A135" s="6" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4085,19 +4085,19 @@
       <c r="A137" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4117,129 +4117,154 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="28" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+    <row r="142" ht="28" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr"/>
-      <c r="E141" s="4" t="inlineStr"/>
-    </row>
-    <row r="142" ht="26" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143" ht="26" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B142" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="C142" s="7" t="inlineStr">
+      <c r="B143" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D142" s="7" t="inlineStr"/>
-      <c r="E142" s="7" t="inlineStr"/>
-    </row>
-    <row r="143" ht="26" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr"/>
       <c r="E143" s="7" t="inlineStr"/>
     </row>
     <row r="144" ht="26" customHeight="1">
-      <c r="A144" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B144" s="6" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr"/>
       <c r="E144" s="7" t="inlineStr"/>
     </row>
     <row r="145" ht="26" customHeight="1">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B145" s="6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr"/>
       <c r="E145" s="7" t="inlineStr"/>
     </row>
     <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="12" t="inlineStr">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr"/>
+      <c r="E146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B146" s="13" t="n">
-        <v>134</v>
-      </c>
-      <c r="C146" s="14" t="inlineStr"/>
-      <c r="D146" s="14" t="inlineStr"/>
-      <c r="E146" s="14" t="inlineStr"/>
-    </row>
-    <row r="148" ht="76" customHeight="1">
-      <c r="A148" s="11" t="inlineStr">
+      <c r="B147" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="C147" s="14" t="inlineStr"/>
+      <c r="D147" s="14" t="inlineStr"/>
+      <c r="E147" s="14" t="inlineStr"/>
+    </row>
+    <row r="149" ht="76" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4249,8 +4274,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A148:E148"/>
+    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="A141:E141"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月8日の事前打合せ（構成3町への町別ヒアリングの前に広域連合と受託者で行うもの）で用いる資料。仮置きによる算定の結果、事前にお決めいただきたい事項（確認先が広域連合であり影響度の点が4点以上のもの）、ヒアリングで構成3町へ伺う事項（町別及び3町共通）と町からご提供をお願いする資料、保険料の月額を動かす前提、ヒアリングの進め方を1枚にまとめたもの。ヒアリングの場で用いる資料は「3町ヒアリング資料」及び「10月 地域課題の整理と3町協議の確認事項」による</t>
+          <t>令和8年10月8日の事前打合せ（構成3町への町別ヒアリングの前に広域連合と受託者で行うもの）で用いる資料。打合せが1〜2時間であることを踏まえ、この場で決めるものをA群・B群・C群に分けて所要の目安を分で付した最低限の確認事項と時間配分（90分の案・120分の案）、仮置きによる算定の結果、事前にお決めいただきたい事項、ヒアリングで構成3町へ伺う事項（町別及び3町共通）と町からご提供をお願いする資料、保険料の月額を動かす前提、ヒアリングの進め方を1枚にまとめたもの。ヒアリングの場で用いる資料は「3町ヒアリング資料」及び「10月 地域課題の整理と3町協議の確認事項」による</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月上旬の構成3町合同の意見交換会で用いる資料。第10期計画の策定の状況、サービス見込量・給付費・保険料の試算（第1次概算）、保険料の月額を動かす前提、地域課題15件、3町共通の確認事項、認知症施策推進計画の扱い、資料のご提供のお願い及び10月以降の工程を1冊にまとめたもの。ご決定をお願いする事項には、すべて「決まらない場合の当方の扱い」（受託者の仮置き）を置いており、うち計画素案へ反映した6件は反映した内容を併せて掲げている。町ごとの個別協議の確認事項は「10月 地域課題の整理と3町協議の確認事項」による</t>
+          <t>令和8年10月上旬の構成3町合同の意見交換会で用いる資料。次第と時間配分の案（120分の場合・90分の場合）、第10期計画の策定の状況、サービス見込量・給付費・保険料の試算、保険料の月額を動かす前提、令和8年9月18日の社会保障審議会介護保険部会で示された事項のうち構成3町に関わるもの、地域課題15件、3町共通の確認事項、認知症施策推進計画の扱い、資料のご提供のお願い及び10月以降の工程を1冊にまとめたもの。3町共通の確認事項は、この場でご決定をお願いしたいもの（A群）・時間があればご決定をお願いしたいもの（B群）・仮置きのまま進めるもの（C群）に分け、所要の目安を分で付している。A群は4つの観点（3町の意向がないと計画の記載が確定しない／月額への効きが大きい／法定記載事項に直結する／第2次概算の前提になる）のうち2つ以上に当たるものとした。ご決定をお願いする事項には、すべて「決まらない場合の当方の扱い」（受託者の仮置き）を置いており、計画素案へ反映した事項は反映した内容を併せて掲げている。町ごとの個別協議の確認事項は「10月 地域課題の整理と3町協議の確認事項」による</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2135,19 +2135,19 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_介護給付費分科会の論点整理の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>社会保障審議会介護給付費分科会（第256回から第270回）において令和9年度介護報酬改定に向けて検討されている論点31件を、計画素案・サービス見込量の算定・確認事項の台帳と突き合わせたもの。当区域に直結するものが17件あり、うち特に当区域の事情に関わるものとして短期入所生活介護の季節利用に係る例外（積雪期）、夜間対応型訪問介護の定期巡回への移行（移行猶予 令和11年3月）、高齢者向け住まいに係る通所介護等の報酬区分の見直し、特定地域における配置の弾力化、特別養護老人ホームの指定定員と実際の受入能力の差の5件を掲げている。国の公表の予定は、改定の考え方及び運営基準に関する整理が令和8年12月頃、諮問及び答申が令和9年1月頃であり、いずれも第2次概算（令和8年10月30日）より後である。検討されている事項はいずれも算定を止めるものではなく、量は令和7年度の実績により算定し、単価及び制度は現行制度で算定したうえで確定情報により再算定する。資料の原本を確認できていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない（確認事項No.182）</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2185,19 +2185,19 @@
       <c r="A61" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2260,19 +2260,19 @@
       <c r="A64" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2310,19 +2310,19 @@
       <c r="A66" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2335,19 +2335,19 @@
       <c r="A67" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2385,19 +2385,19 @@
       <c r="A69" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表データ管理台帳.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_図表データ管理台帳.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2760,19 +2760,19 @@
       <c r="A84" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2785,19 +2785,19 @@
       <c r="A85" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2985,19 +2985,19 @@
       <c r="A93" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,19 +3285,19 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3410,19 +3410,19 @@
       <c r="A110" s="6" t="n">
         <v>106</v>
       </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3535,19 +3535,19 @@
       <c r="A115" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3610,19 +3610,19 @@
       <c r="A118" s="6" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3635,19 +3635,19 @@
       <c r="A119" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3685,19 +3685,19 @@
       <c r="A121" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,19 +3710,19 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3735,19 +3735,19 @@
       <c r="A123" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3810,19 +3810,19 @@
       <c r="A126" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3835,19 +3835,19 @@
       <c r="A127" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3860,19 +3860,19 @@
       <c r="A128" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3935,19 +3935,19 @@
       <c r="A131" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3960,19 +3960,19 @@
       <c r="A132" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4010,19 +4010,19 @@
       <c r="A134" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4035,19 +4035,19 @@
       <c r="A135" s="6" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4060,19 +4060,19 @@
       <c r="A136" s="6" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4110,19 +4110,19 @@
       <c r="A138" s="6" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4142,129 +4142,154 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="28" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
+    <row r="143" ht="28" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr"/>
-      <c r="E142" s="4" t="inlineStr"/>
-    </row>
-    <row r="143" ht="26" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144" ht="26" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B143" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="B144" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="inlineStr"/>
-      <c r="E143" s="7" t="inlineStr"/>
-    </row>
-    <row r="144" ht="26" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C144" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr"/>
       <c r="E144" s="7" t="inlineStr"/>
     </row>
     <row r="145" ht="26" customHeight="1">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B145" s="6" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr"/>
       <c r="E145" s="7" t="inlineStr"/>
     </row>
     <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B146" s="6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr"/>
       <c r="E146" s="7" t="inlineStr"/>
     </row>
     <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="12" t="inlineStr">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr"/>
+      <c r="E147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148" ht="26" customHeight="1">
+      <c r="A148" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B147" s="13" t="n">
-        <v>135</v>
-      </c>
-      <c r="C147" s="14" t="inlineStr"/>
-      <c r="D147" s="14" t="inlineStr"/>
-      <c r="E147" s="14" t="inlineStr"/>
-    </row>
-    <row r="149" ht="76" customHeight="1">
-      <c r="A149" s="11" t="inlineStr">
+      <c r="B148" s="13" t="n">
+        <v>136</v>
+      </c>
+      <c r="C148" s="14" t="inlineStr"/>
+      <c r="D148" s="14" t="inlineStr"/>
+      <c r="E148" s="14" t="inlineStr"/>
+    </row>
+    <row r="150" ht="76" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4274,8 +4299,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A149:E149"/>
-    <mergeCell ref="A141:E141"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A142:E142"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>社会保障審議会介護給付費分科会（第256回から第270回）において令和9年度介護報酬改定に向けて検討されている論点31件を、計画素案・サービス見込量の算定・確認事項の台帳と突き合わせたもの。当区域に直結するものが17件あり、うち特に当区域の事情に関わるものとして短期入所生活介護の季節利用に係る例外（積雪期）、夜間対応型訪問介護の定期巡回への移行（移行猶予 令和11年3月）、高齢者向け住まいに係る通所介護等の報酬区分の見直し、特定地域における配置の弾力化、特別養護老人ホームの指定定員と実際の受入能力の差の5件を掲げている。国の公表の予定は、改定の考え方及び運営基準に関する整理が令和8年12月頃、諮問及び答申が令和9年1月頃であり、いずれも第2次概算（令和8年10月30日）より後である。検討されている事項はいずれも算定を止めるものではなく、量は令和7年度の実績により算定し、単価及び制度は現行制度で算定したうえで確定情報により再算定する。資料の原本を確認できていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない（確認事項No.182）</t>
+          <t>社会保障審議会介護給付費分科会（第256回から第270回）において令和9年度介護報酬改定に向けて検討されている論点31件を、計画素案・サービス見込量の算定・確認事項の台帳と突き合わせたもの。当区域に直結するものが17件あり、うち特に当区域の事情に関わるものとして短期入所生活介護の季節利用に係る例外（積雪期）、夜間対応型訪問介護の定期巡回への移行（移行猶予 令和11年3月）、高齢者向け住まいに係る通所介護等の報酬区分の見直し、特定地域における配置の弾力化、特別養護老人ホームの指定定員と実際の受入能力の差の5件を掲げている。国の公表の予定は、改定の考え方及び運営基準に関する整理が令和8年12月頃、諮問及び答申が令和9年1月頃であり、いずれも第2次概算（令和8年10月30日）より後である。検討されている事項はいずれも算定を止めるものではなく、量は令和7年度の実績により算定し、単価及び制度は現行制度で算定したうえで確定情報により再算定する。本整理に資料の原本は同梱されていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない（確認事項No.182）。原典による確認は別冊「介護給付費分科会資料（原典）の受領点検」による</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2160,19 +2160,19 @@
       <c r="A60" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料11件（第268回 基本的な視点（案）、第269回 資料1から資料4、第270回 資料1から資料5。全311頁）を読み、当方の論点の整理と突き合わせたもの。論点7件を原典により確かめ、1件に是正を要することが分かり、整理にない12件が新たに分かった。是正したのは夜間対応型訪問介護の経過措置の期限であり、原典の中に令和11年度末までとするものと令和11年3月までとするものの2通りの記載がある。新たに分かったもののうち当区域に関わるものは、生産性向上推進のための協議会の設置が都道府県の義務となったこと、中山間地域の加算のあり方の見直し、短期入所療養介護への長期利用減算の新設、中山間地域等における入浴介助を目的とするサービスの特例、認知症対応型通所介護の基本報酬の在り方である。計画素案は9箇所を改めた</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2210,19 +2210,19 @@
       <c r="A62" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2285,19 +2285,19 @@
       <c r="A65" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2335,19 +2335,19 @@
       <c r="A67" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2360,19 +2360,19 @@
       <c r="A68" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表データ管理台帳.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_図表データ管理台帳.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2610,19 +2610,19 @@
       <c r="A78" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2660,19 +2660,19 @@
       <c r="A80" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2785,19 +2785,19 @@
       <c r="A85" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2810,19 +2810,19 @@
       <c r="A86" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2885,19 +2885,19 @@
       <c r="A89" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2985,19 +2985,19 @@
       <c r="A93" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3410,19 +3410,19 @@
       <c r="A110" s="6" t="n">
         <v>106</v>
       </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3510,19 +3510,19 @@
       <c r="A114" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3635,19 +3635,19 @@
       <c r="A119" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,19 +3710,19 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3735,19 +3735,19 @@
       <c r="A123" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3810,19 +3810,19 @@
       <c r="A126" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3835,19 +3835,19 @@
       <c r="A127" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3860,19 +3860,19 @@
       <c r="A128" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3885,19 +3885,19 @@
       <c r="A129" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3960,19 +3960,19 @@
       <c r="A132" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3985,19 +3985,19 @@
       <c r="A133" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4035,19 +4035,19 @@
       <c r="A135" s="6" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4060,19 +4060,19 @@
       <c r="A136" s="6" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4085,19 +4085,19 @@
       <c r="A137" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4117,12 +4117,12 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4135,19 +4135,19 @@
       <c r="A139" s="6" t="n">
         <v>135</v>
       </c>
-      <c r="B139" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4167,129 +4167,154 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="28" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+    <row r="144" ht="28" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr"/>
-      <c r="E143" s="4" t="inlineStr"/>
-    </row>
-    <row r="144" ht="26" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr"/>
+      <c r="E144" s="4" t="inlineStr"/>
+    </row>
+    <row r="145" ht="26" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="C144" s="7" t="inlineStr">
+      <c r="B145" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D144" s="7" t="inlineStr"/>
-      <c r="E144" s="7" t="inlineStr"/>
-    </row>
-    <row r="145" ht="26" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C145" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr"/>
       <c r="E145" s="7" t="inlineStr"/>
     </row>
     <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B146" s="6" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr"/>
       <c r="E146" s="7" t="inlineStr"/>
     </row>
     <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B147" s="6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr"/>
       <c r="E147" s="7" t="inlineStr"/>
     </row>
     <row r="148" ht="26" customHeight="1">
-      <c r="A148" s="12" t="inlineStr">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr"/>
+      <c r="E148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149" ht="26" customHeight="1">
+      <c r="A149" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B148" s="13" t="n">
-        <v>136</v>
-      </c>
-      <c r="C148" s="14" t="inlineStr"/>
-      <c r="D148" s="14" t="inlineStr"/>
-      <c r="E148" s="14" t="inlineStr"/>
-    </row>
-    <row r="150" ht="76" customHeight="1">
-      <c r="A150" s="11" t="inlineStr">
+      <c r="B149" s="13" t="n">
+        <v>137</v>
+      </c>
+      <c r="C149" s="14" t="inlineStr"/>
+      <c r="D149" s="14" t="inlineStr"/>
+      <c r="E149" s="14" t="inlineStr"/>
+    </row>
+    <row r="151" ht="76" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4299,8 +4324,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A150:E150"/>
-    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A143:E143"/>
+    <mergeCell ref="A151:E151"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料11件（第268回 基本的な視点（案）、第269回 資料1から資料4、第270回 資料1から資料5。全311頁）を読み、当方の論点の整理と突き合わせたもの。論点7件を原典により確かめ、1件に是正を要することが分かり、整理にない12件が新たに分かった。是正したのは夜間対応型訪問介護の経過措置の期限であり、原典の中に令和11年度末までとするものと令和11年3月までとするものの2通りの記載がある。新たに分かったもののうち当区域に関わるものは、生産性向上推進のための協議会の設置が都道府県の義務となったこと、中山間地域の加算のあり方の見直し、短期入所療養介護への長期利用減算の新設、中山間地域等における入浴介助を目的とするサービスの特例、認知症対応型通所介護の基本報酬の在り方である。計画素案は9箇所を改めた</t>
+          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料25件（第262回 資料1から資料4、第263回 資料1から資料5、第264回 資料1から資料5、第268回 基本的な視点（案）、第269回 資料1から資料4、第270回 資料1から資料5。全1,037頁）を読み、当方の論点の整理と突き合わせたもの。論点7件を原典により確かめ、1件に是正を要することが分かり、整理にない21件が新たに分かった。是正したのは夜間対応型訪問介護の経過措置の期限であり、原典の中に令和11年度末までとするものと令和11年3月までとするものの2通りの記載がある。新たに分かったもののうち当区域に関わるものは、登録施設介護（予防）支援の施行日が令和9年4月1日ではないこと（公布の日から3年を超えない範囲内の政令で定める日）、地域区分の広域連合ルールと令和9年度改定における広域化の検討、同一建物等居住者へのサービス提供の実態、生産性向上推進のための協議会の設置が都道府県の義務となったこと、中山間地域に係る加算が3種類あること、短期入所療養介護への長期利用減算の新設、中山間地域等における入浴介助を目的とするサービスの特例、業務継続に係る市町村の助言等の状況である。計画素案は16箇所を改めた</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3535,19 +3535,19 @@
       <c r="A115" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,19 +3585,19 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3685,19 +3685,19 @@
       <c r="A121" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3735,19 +3735,19 @@
       <c r="A123" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3810,19 +3810,19 @@
       <c r="A126" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3835,19 +3835,19 @@
       <c r="A127" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3860,19 +3860,19 @@
       <c r="A128" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3885,19 +3885,19 @@
       <c r="A129" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3910,19 +3910,19 @@
       <c r="A130" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3985,19 +3985,19 @@
       <c r="A133" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4010,19 +4010,19 @@
       <c r="A134" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4060,19 +4060,19 @@
       <c r="A136" s="6" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4085,19 +4085,19 @@
       <c r="A137" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4110,19 +4110,19 @@
       <c r="A138" s="6" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4160,19 +4160,19 @@
       <c r="A140" s="6" t="n">
         <v>136</v>
       </c>
-      <c r="B140" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -4192,129 +4192,154 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr">
+      <c r="D142" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="28" customHeight="1">
-      <c r="A144" s="4" t="inlineStr">
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr"/>
-      <c r="E144" s="4" t="inlineStr"/>
-    </row>
-    <row r="145" ht="26" customHeight="1">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="D145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr"/>
+    </row>
+    <row r="146" ht="26" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>送付</t>
         </is>
       </c>
-      <c r="B145" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="B146" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D145" s="7" t="inlineStr"/>
-      <c r="E145" s="7" t="inlineStr"/>
-    </row>
-    <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C146" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr"/>
       <c r="E146" s="7" t="inlineStr"/>
     </row>
     <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B147" s="6" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr"/>
       <c r="E147" s="7" t="inlineStr"/>
     </row>
     <row r="148" ht="26" customHeight="1">
-      <c r="A148" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B148" s="6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr"/>
       <c r="E148" s="7" t="inlineStr"/>
     </row>
     <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="12" t="inlineStr">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150" ht="26" customHeight="1">
+      <c r="A150" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B149" s="13" t="n">
-        <v>137</v>
-      </c>
-      <c r="C149" s="14" t="inlineStr"/>
-      <c r="D149" s="14" t="inlineStr"/>
-      <c r="E149" s="14" t="inlineStr"/>
-    </row>
-    <row r="151" ht="76" customHeight="1">
-      <c r="A151" s="11" t="inlineStr">
+      <c r="B150" s="13" t="n">
+        <v>138</v>
+      </c>
+      <c r="C150" s="14" t="inlineStr"/>
+      <c r="D150" s="14" t="inlineStr"/>
+      <c r="E150" s="14" t="inlineStr"/>
+    </row>
+    <row r="152" ht="76" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4324,8 +4349,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A143:E143"/>
-    <mergeCell ref="A151:E151"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A152:E152"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2985,19 +2985,19 @@
       <c r="A93" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_改正後の条文及び特定地域の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>令和8年10月15日に受領した社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）、特定地域（中山間・人口減少地域）の考え方について（社会保障審議会介護保険部会 第135回 資料3）及び介護保険における3つの加算の対象地域一覧を読み、当方の整理と突き合わせたもの。従前は法律案要綱により整理していたため号及び項の一部を［要確認］としていたが、改正後の介護保険法第117条、第115条の48（支援会議）、第118条第2項及び第120条の3から第120条の5まで（協議会）の内容が確定した。中長期的な推計は、量が定めるものとされる事項（第2項第3号）、費用の額及び保険料の水準が定めるよう努めるものとされる事項（第3項第3号）であり義務の程度が異なる。あわせて、特別地域加算の対象地域に構成3町がいずれも掲げられていないこと（確認事項No.1の解決）と、北海道は全域が豪雪地帯であるため中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の地域の要件には該当することを確認した。計画素案15箇所を改めた。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,19 +3285,19 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3610,19 +3610,19 @@
       <c r="A118" s="6" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3685,19 +3685,19 @@
       <c r="A121" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,19 +3710,19 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3810,19 +3810,19 @@
       <c r="A126" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3835,19 +3835,19 @@
       <c r="A127" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3860,19 +3860,19 @@
       <c r="A128" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3885,19 +3885,19 @@
       <c r="A129" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3910,19 +3910,19 @@
       <c r="A130" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3935,19 +3935,19 @@
       <c r="A131" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4010,19 +4010,19 @@
       <c r="A134" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4035,19 +4035,19 @@
       <c r="A135" s="6" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4085,19 +4085,19 @@
       <c r="A137" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4110,19 +4110,19 @@
       <c r="A138" s="6" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4135,19 +4135,19 @@
       <c r="A139" s="6" t="n">
         <v>135</v>
       </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -4185,19 +4185,19 @@
       <c r="A141" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4217,129 +4217,154 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="28" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr"/>
-      <c r="E145" s="4" t="inlineStr"/>
-    </row>
-    <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="C146" s="7" t="inlineStr">
+      <c r="D146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr"/>
+    </row>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D146" s="7" t="inlineStr"/>
-      <c r="E146" s="7" t="inlineStr"/>
-    </row>
-    <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C147" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr"/>
       <c r="E147" s="7" t="inlineStr"/>
     </row>
     <row r="148" ht="26" customHeight="1">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B148" s="6" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr"/>
       <c r="E148" s="7" t="inlineStr"/>
     </row>
     <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B149" s="6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr"/>
       <c r="E149" s="7" t="inlineStr"/>
     </row>
     <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="12" t="inlineStr">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr"/>
+      <c r="E150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151" ht="26" customHeight="1">
+      <c r="A151" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B150" s="13" t="n">
-        <v>138</v>
-      </c>
-      <c r="C150" s="14" t="inlineStr"/>
-      <c r="D150" s="14" t="inlineStr"/>
-      <c r="E150" s="14" t="inlineStr"/>
-    </row>
-    <row r="152" ht="76" customHeight="1">
-      <c r="A152" s="11" t="inlineStr">
+      <c r="B151" s="13" t="n">
+        <v>139</v>
+      </c>
+      <c r="C151" s="14" t="inlineStr"/>
+      <c r="D151" s="14" t="inlineStr"/>
+      <c r="E151" s="14" t="inlineStr"/>
+    </row>
+    <row r="153" ht="76" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4349,8 +4374,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A144:E144"/>
-    <mergeCell ref="A152:E152"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A153:E153"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表データ管理台帳.xlsx</t>
+          <t>第10期計画_参照条文の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
+          <t>令和8年10月15日に受領した参照条文（社会福祉法等の一部を改正する法律案。全45頁・16法令）の文字起こしを読み、当方の整理と突き合わせたもの。原本は条文の部分が画像であって文字の層がなく読み取れなかったが、文字起こしのご提供により介護保険法第117条の項の全体（全14項）及び第3項の全10号、第118条並びに第115条の45の項及び号を確認した（確認事項No.181の解決）。従前の記述の誤りが5件分かった。うち重いものは、医療計画及び地域医療構想との整合性の確保は都道府県介護保険事業支援計画の義務（第118条第10項）であって市町村介護保険事業計画の義務ではないこと（市町村計画が整合性を確保すべき相手は地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項の市町村計画である）と、混合型及び介護専用型の特定施設入居者生活介護に係る必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（第118条第2項第1号・第4項）であって本計画の記載事項ではないこと（確認事項No.113の解決）の2件である。新たに分かったものは10件で、地域支援事業費に政令上の上限があること（第115条の45第4項）、介護老人保健施設の開設の許可に当たって北海道知事が本計画との調整を図る見地からの意見を求めなければならないこと（第94条第6項）を含む。文字起こしは未校正の光学文字認識によるものであるため、条、項及び号の番号を用い条文の文言は計画素案に引用しない。確からしさは新旧対照条文との突合6件により確かめている。収録されている介護保険法は医療法等の一部を改正する法律（令和7年法律第87号）による改正後の未施行の版である。</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_図表データ管理台帳.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2635,19 +2635,19 @@
       <c r="A79" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2685,19 +2685,19 @@
       <c r="A81" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2810,19 +2810,19 @@
       <c r="A86" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2885,19 +2885,19 @@
       <c r="A89" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2985,19 +2985,19 @@
       <c r="A93" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_改正後の条文及び特定地域の受領点検.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月15日に受領した社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）、特定地域（中山間・人口減少地域）の考え方について（社会保障審議会介護保険部会 第135回 資料3）及び介護保険における3つの加算の対象地域一覧を読み、当方の整理と突き合わせたもの。従前は法律案要綱により整理していたため号及び項の一部を［要確認］としていたが、改正後の介護保険法第117条、第115条の48（支援会議）、第118条第2項及び第120条の3から第120条の5まで（協議会）の内容が確定した。中長期的な推計は、量が定めるものとされる事項（第2項第3号）、費用の額及び保険料の水準が定めるよう努めるものとされる事項（第3項第3号）であり義務の程度が異なる。あわせて、特別地域加算の対象地域に構成3町がいずれも掲げられていないこと（確認事項No.1の解決）と、北海道は全域が豪雪地帯であるため中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の地域の要件には該当することを確認した。計画素案15箇所を改めた。</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_改正後の条文及び特定地域の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>令和8年10月15日に受領した社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）、特定地域（中山間・人口減少地域）の考え方について（社会保障審議会介護保険部会 第135回 資料3）及び介護保険における3つの加算の対象地域一覧を読み、当方の整理と突き合わせたもの。従前は法律案要綱により整理していたため号及び項の一部を［要確認］としていたが、改正後の介護保険法第117条、第115条の48（支援会議）、第118条第2項及び第120条の3から第120条の5まで（協議会）の内容が確定した。中長期的な推計は、量が定めるものとされる事項（第2項第3号）、費用の額及び保険料の水準が定めるよう努めるものとされる事項（第3項第3号）であり義務の程度が異なる。あわせて、特別地域加算の対象地域に構成3町がいずれも掲げられていないこと（確認事項No.1の解決）と、北海道は全域が豪雪地帯であるため中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の地域の要件には該当することを確認した。計画素案15箇所を改めた。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認事項の資料徴求と公表資料による確認.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>ご決定・ご確認をお待ちしている事項の一覧を、何をすれば決着するかという軸で区分したもの。A 広域連合（及び構成3町等）から資料の徴求を要するもの、B 公表資料により確認できるもの、B待 公表を待つもの（国の政令・省令・告示）、C ご判断・ご決定を求めるもの、D 資料の徴求を要しないものの5区分による。区分Aの全件に資料が届かない場合の扱いを付し、①安全側の置き方で算定する、②未確定箇所として残す、③当該の記載を掲げない、④現に確認できている値で確定するの4つに分けた。区分Aのうち大半は資料が届かなくても計画本文を確定でき、未確定箇所の記号が残るものは限られる。優先してご提供をお願いするものを、保険料の月額に効くもの、介護保険法第117条に関わるもの、影響度の高いもの及び資料が届かないと計画の記載に跡が残るものの4つの観点で掲げた。資料が届かない場合の扱いは受託者の仮置きであり決定ではない。</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3285,19 +3285,19 @@
       <c r="A105" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3310,19 +3310,19 @@
       <c r="A106" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3535,19 +3535,19 @@
       <c r="A115" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,19 +3585,19 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3610,19 +3610,19 @@
       <c r="A118" s="6" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3635,19 +3635,19 @@
       <c r="A119" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,19 +3710,19 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。**必要資料が未受領であることによる暫定値であり確定値ではない。**その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。必要資料が未受領であることによる暫定値であり確定値ではない。その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3810,19 +3810,19 @@
       <c r="A126" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3835,19 +3835,19 @@
       <c r="A127" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3860,19 +3860,19 @@
       <c r="A128" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3885,19 +3885,19 @@
       <c r="A129" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3910,19 +3910,19 @@
       <c r="A130" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3985,19 +3985,19 @@
       <c r="A133" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4035,19 +4035,19 @@
       <c r="A135" s="6" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4085,19 +4085,19 @@
       <c r="A137" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4110,19 +4110,19 @@
       <c r="A138" s="6" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -4185,19 +4185,19 @@
       <c r="A141" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4210,19 +4210,19 @@
       <c r="A142" s="6" t="n">
         <v>138</v>
       </c>
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -4235,136 +4235,186 @@
       <c r="A143" s="6" t="n">
         <v>139</v>
       </c>
-      <c r="B143" s="9" t="inlineStr">
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
+      <c r="D145" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="28" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr"/>
-      <c r="E146" s="4" t="inlineStr"/>
-    </row>
-    <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="C147" s="7" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr"/>
+    </row>
+    <row r="149" ht="26" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D147" s="7" t="inlineStr"/>
-      <c r="E147" s="7" t="inlineStr"/>
-    </row>
-    <row r="148" ht="26" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C148" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
-        </is>
-      </c>
-      <c r="D148" s="7" t="inlineStr"/>
-      <c r="E148" s="7" t="inlineStr"/>
-    </row>
-    <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="C149" s="7" t="inlineStr">
-        <is>
-          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr"/>
       <c r="E149" s="7" t="inlineStr"/>
     </row>
     <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B150" s="6" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr"/>
       <c r="E150" s="7" t="inlineStr"/>
     </row>
     <row r="151" ht="26" customHeight="1">
-      <c r="A151" s="12" t="inlineStr">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>納品時又は求めに応じて提出する</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr"/>
+      <c r="E151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152" ht="26" customHeight="1">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr"/>
+      <c r="E152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153" ht="26" customHeight="1">
+      <c r="A153" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B151" s="13" t="n">
-        <v>139</v>
-      </c>
-      <c r="C151" s="14" t="inlineStr"/>
-      <c r="D151" s="14" t="inlineStr"/>
-      <c r="E151" s="14" t="inlineStr"/>
-    </row>
-    <row r="153" ht="76" customHeight="1">
-      <c r="A153" s="11" t="inlineStr">
+      <c r="B153" s="13" t="n">
+        <v>141</v>
+      </c>
+      <c r="C153" s="14" t="inlineStr"/>
+      <c r="D153" s="14" t="inlineStr"/>
+      <c r="E153" s="14" t="inlineStr"/>
+    </row>
+    <row r="155" ht="76" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4374,8 +4424,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A145:E145"/>
-    <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A155:E155"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>第10期介護保険事業計画_骨子案.docx</t>
+          <t>第10期介護保険事業計画_概要版.docx</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>章立てと根拠資料の対照。決定・確認を要する事項12件を含む</t>
+          <t>A4判8頁。パブリックコメント（令和9年1月・2週間）及び住民の皆様への周知に用いる。別冊「第10期計画_概要版の構成案」の頁割・掲載内容により組み立て、協議用素案から数値を引いている（本文・数値を別に持たない）。本編の文はそのまま採らず、住民の皆様に向けて書き直している（基本理念及び基本目標の名称は本編と同一の表現とする）。ご意見を求める論点6件を各頁に、本編の該当頁の案内を各頁末に置く。頁数・判型・体裁・保険料の掲載の範囲は構成案の決定を要するため、受託者の案によっている。保険料は試算であり、目標の値を定めていない指標は「検討中」と記載している。未確定箇所が残る間は表題を「（素案）の概要」とする</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1035,19 +1035,19 @@
       <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx</t>
+          <t>第10期介護保険事業計画_骨子案.docx</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月工程の「地域課題整理資料」と「3町協議資料」。地域課題15件を根拠となる数値・出所・計画本文の反映先と対にして掲げ、町ごとの確認事項（東川町・美瑛町・東神楽町）と3町共通の確認事項を業務工程管理表から読んで一覧にした。認知症基本法第13条の市町村認知症施策推進計画（案B）について、保険者機能強化推進交付金等の認知症総合支援の町別評価を踏まえ、各町で決めていただく事項を掲げている。全ての確認事項に「決まらない場合の当方の扱い」を置いている</t>
+          <t>章立てと根拠資料の対照。決定・確認を要する事項12件を含む</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
+          <t>第10期計画_10月 地域課題の整理と3町協議の確認事項.xlsx</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
+          <t>令和8年10月工程の「地域課題整理資料」と「3町協議資料」。地域課題15件を根拠となる数値・出所・計画本文の反映先と対にして掲げ、町ごとの確認事項（東川町・美瑛町・東神楽町）と3町共通の確認事項を業務工程管理表から読んで一覧にした。認知症基本法第13条の市町村認知症施策推進計画（案B）について、保険者機能強化推進交付金等の認知症総合支援の町別評価を踏まえ、各町で決めていただく事項を掲げている。全ての確認事項に「決まらない場合の当方の扱い」を置いている</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1085,19 +1085,19 @@
       <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町ヒアリング資料.docx</t>
+          <t>第10期計画_3町の社会資源一覧との突合.xlsx</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>3町へのヒアリング資料。設問はご確認を要する</t>
+          <t>3町提供の社会資源一覧との突合。計画素案とサービスガイド構成案の事業所の整合（06シート）を含む。担当者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町別の論点整理.xlsx</t>
+          <t>第10期計画_3町ヒアリング資料.docx</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
+          <t>3町へのヒアリング資料。設問はご確認を要する</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1135,19 +1135,19 @@
       <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_3町合同意見交換会資料.docx</t>
+          <t>第10期計画_3町別の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月上旬の構成3町合同の意見交換会で用いる資料。次第と時間配分の案（120分の場合・90分の場合）、第10期計画の策定の状況、サービス見込量・給付費・保険料の試算、保険料の月額を動かす前提、令和8年9月18日の社会保障審議会介護保険部会で示された事項のうち構成3町に関わるもの、地域課題15件、3町共通の確認事項、認知症施策推進計画の扱い、資料のご提供のお願い及び10月以降の工程を1冊にまとめたもの。3町共通の確認事項は、この場でご決定をお願いしたいもの（A群）・時間があればご決定をお願いしたいもの（B群）・仮置きのまま進めるもの（C群）に分け、所要の目安を分で付している。A群は4つの観点（3町の意向がないと計画の記載が確定しない／月額への効きが大きい／法定記載事項に直結する／第2次概算の前提になる）のうち2つ以上に当たるものとした。ご決定をお願いする事項には、すべて「決まらない場合の当方の扱い」（受託者の仮置き）を置いており、計画素案へ反映した事項は反映した内容を併せて掲げている。町ごとの個別協議の確認事項は「10月 地域課題の整理と3町協議の確認事項」による</t>
+          <t>令和8年10月・11月の3町協議に向けた論点整理。町別の現在地、総合事業の町別実施状況、交付金の町別得点、町ごとの論点19件、3町共通の論点9件、協議の進め方。議題の取捨と順序は発注者のご判断による</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
+          <t>第10期計画_3町合同意見交換会資料.docx</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
+          <t>令和8年10月上旬の構成3町合同の意見交換会で用いる資料。次第と時間配分の案（120分の場合・90分の場合）、第10期計画の策定の状況、サービス見込量・給付費・保険料の試算、保険料の月額を動かす前提、令和8年9月18日の社会保障審議会介護保険部会で示された事項のうち構成3町に関わるもの、地域課題15件、3町共通の確認事項、認知症施策推進計画の扱い、資料のご提供のお願い及び10月以降の工程を1冊にまとめたもの。3町共通の確認事項は、この場でご決定をお願いしたいもの（A群）・時間があればご決定をお願いしたいもの（B群）・仮置きのまま進めるもの（C群）に分け、所要の目安を分で付している。A群は4つの観点（3町の意向がないと計画の記載が確定しない／月額への効きが大きい／法定記載事項に直結する／第2次概算の前提になる）のうち2つ以上に当たるものとした。ご決定をお願いする事項には、すべて「決まらない場合の当方の扱い」（受託者の仮置き）を置いており、計画素案へ反映した事項は反映した内容を併せて掲げている。町ごとの個別協議の確認事項は「10月 地域課題の整理と3町協議の確認事項」による</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1185,19 +1185,19 @@
       <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート分析_点検箇所と手順.docx</t>
+          <t>第10期計画_9月作業_アンケート分析の作業状況.xlsx</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>アンケート調査の分析について、この業務に携わっていない者が点検するための資料（全10節）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。成果品のシート数・段落数は実物を開いて数え、自己点検の件数はソースの呼出しを数え、留保・所見は集計分析報告書によっている。特に見る箇所として、母集団の書き方、在籍と受給の書き分け、率と実数の併記、見込量のじか書き、反映済みの判定、留保の落とし、個票の非収録を挙げた。この作業で実際に起きた誤り7件を、気づいた経緯と手立てとともに掲げた。個人情報は値の形（正規表現）で、禁止表現は語で探す方法を示している。点検の記録様式と分担の案を含む</t>
+          <t>令和8年9月工程のうちアンケート調査の集計・分析について作業状況を整理したもの。完了した作業、未了の作業と着手の条件、発注者のご判断を待っている事項4件、9月内の作業工程</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1210,19 +1210,19 @@
       <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
+          <t>第10期計画_アンケート分析_点検箇所と手順.docx</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案 第2章第4節への反映、調査結果と保険者の実績（年報 令和7年度）の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保をまとめている。9月に新たにできるようになったのは、年報の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違う。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠はいずれも成果品によっており、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。ご判断をお願いする事項3件を含む</t>
+          <t>アンケート調査の分析について、この業務に携わっていない者が点検するための資料（全10節）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。成果品のシート数・段落数は実物を開いて数え、自己点検の件数はソースの呼出しを数え、留保・所見は集計分析報告書によっている。特に見る箇所として、母集団の書き方、在籍と受給の書き分け、率と実数の併記、見込量のじか書き、反映済みの判定、留保の落とし、個票の非収録を挙げた。この作業で実際に起きた誤り7件を、気づいた経緯と手立てとともに掲げた。個人情報は値の形（正規表現）で、禁止表現は語で探す方法を示している。点検の記録様式と分担の案を含む</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
+          <t>第10期計画_アンケート調査の分析_令和8年9月業務報告.docx</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>4調査の集計。限界と留保を各シートに明記している</t>
+          <t>業務仕様書「４．業務内容（3）実施済み調査結果の集計・分析」及び「５．履行工程　令和8年9月」に対する報告（全11節）。令和8年9月に行ったこと、仕様書４（3）の作業項目7件に対する状況、対象4調査の母数と回収の状況、前回調査との比較（経年）、健康とくらしの調査の結果と計画素案 第2章第4節への反映、調査結果と保険者の実績（年報 令和7年度）の突合、調査から把握した地域課題、主要所見の反映状況、調査結果の限界と留保をまとめている。9月に新たにできるようになったのは、年報の要介護度別の明細を収めたことにより調査の結果と保険者の実績を突き合わせられるようになったことである。①在宅生活改善調査は在宅の認定者を代表せず（要介護度分布のχ²＝43.5・自由度6・1％点16.81）、「在宅で困難を抱える方の状況」として引く。②居所変更実態調査の在籍者と年報の受給者は数える対象が違う。認定を受けながらいずれのサービスも利用していない方が認定者の4分の1（486人・24.5％）を占めることを課題として掲げた。件数・区分・留保・所見・課題の根拠はいずれも成果品によっており、見込量は見込量算定（第1次概算）を読んでいるため計画素案 第6章と同じ値になる。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1260,19 +1260,19 @@
       <c r="A24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
+          <t>第10期計画_アンケート調査の集計分析報告書.xlsx</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>進行者の手元資料。会議運営上の想定を含む</t>
+          <t>4調査の集計。限界と留保を各シートに明記している</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
+          <t>第10期計画_キックオフ会議_トークスクリプト_60分.docx</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>進行者の手元資料。想定問答と着地点を含む</t>
+          <t>進行者の手元資料。会議運営上の想定を含む</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1310,19 +1310,19 @@
       <c r="A26" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
+          <t>第10期計画_キックオフ会議_ファシリテーションの分岐.xlsx</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>会議で用いるヒアリングシート</t>
+          <t>進行者の手元資料。想定問答と着地点を含む</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
+          <t>第10期計画_キックオフ会議ヒアリングシート.docx</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>議事録（校正反映後）</t>
+          <t>会議で用いるヒアリングシート</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1360,19 +1360,19 @@
       <c r="A28" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議議事録_令和8年8月6日.odt</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録</t>
+          <t>議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1385,19 +1385,19 @@
       <c r="A29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
+          <t>第10期計画_キックオフ会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>キックオフ会議の配布資料（最新版）</t>
+          <t>受託者による校正の記録</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1410,19 +1410,19 @@
       <c r="A30" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
+          <t>第10期計画_キックオフ会議資料_令和8年8月.docx</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>更新版の作成過程の版。配布は更新版による</t>
+          <t>キックオフ会議の配布資料（最新版）</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料_点検反映版.docx</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録</t>
+          <t>更新版の作成過程の版。配布は更新版による</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
+          <t>第10期計画_キックオフ会議資料（更新版）の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>受託者による会議資料の自己点検の記録</t>
+          <t>受託者による校正の記録</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1485,19 +1485,19 @@
       <c r="A33" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
+          <t>第10期計画_キックオフ資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
+          <t>受託者による会議資料の自己点検の記録</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1510,19 +1510,19 @@
       <c r="A34" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
+          <t>第10期計画_ケアプラン点検実施要領（案）.docx</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>見える化D系列の受領点検</t>
+          <t>介護給付等費用適正化事業として行うケアプランの点検の実施要領の案。計画素案 第5章 基本目標5 の「実施要領の策定（令和9年度当初）」の原案。初年度の点検件数の目安、要介護認定の適正化の実施状況など確定を要する事項7件を含む</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1535,19 +1535,19 @@
       <c r="A35" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定.xlsx</t>
+          <t>第10期計画_サービス受給者数データの確認.xlsx</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料の算定（全18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項を収めている。見込量を掲げるほかの成果品と計画素案 第6章はいずれも本算定による。工程ごとに提示する版は別に残している（第1次概算＝令和8年9月26日、第2次概算＝令和8年10月30日）。決着していない事項は過年度の数値を据え置き、何をどう置いたかを据え置きの一覧に掲げている</t>
+          <t>見える化D系列の受領点検</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
+          <t>第10期計画_サービス見込量の算定.xlsx</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
+          <t>サービス見込量・給付費・保険料の算定（全18シート）。算定の前提、要介護度別の認定者数、サービス見込量（利用者数）、要介護度別の見込量、利用回（日）数、給付費、要介護度別の給付費、在宅と施設の連鎖、施設・居住系と必要利用定員総数、供給の制約（定員上限）と在宅への振替、地域支援事業の量と費用、中長期推計、給付費と保険料、報酬改定率の感度、据え置き・既定値の一覧、自己点検、確認事項を収めている。見込量を掲げるほかの成果品と計画素案 第6章はいずれも本算定による。工程ごとに提示する版は別に残している（第1次概算＝令和8年9月26日、第2次概算＝令和8年10月30日）。決着していない事項は過年度の数値を据え置き、何をどう置いたかを据え置きの一覧に掲げている</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月26日に提示した第1次概算の版。提示した時点の値を残すため、以後は作り直していない（算定を改めた後の値は「第10期計画_サービス見込量の算定.xlsx」による）。いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
+          <t>サービス見込量の算定について、基準年度をどこに置くかを実測により整理し、給付費と保険料への影響を示したもの。数量の基準年度に使えるのは令和7年度だけであること、単価は令和8年度でも使えること、見える化システムの総括表（保険者単位）と計画作成支援ツール（3町合計）で水準が異なることを整理した。算定パターン8件のうち算定できた7件で、算定上の月額基準額は6,224円から7,049円まで825円の幅がある。採用パターン（令和7年度基準・総括表・認定者数シナリオ②）のご判断をお願いする事項2件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量の算定_第2次概算.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第1次概算.xlsx</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>第2次概算（令和8年10月30日）の組立て。第1次概算（令和8年9月26日）からの差分、保険料算定表の記号A〜Jの対照、見込量・利用回（日）数・給付費の種別ごとの差分、中長期推計、月額を動かす前提、見える化システムの出力との対照、残る未決と既定値、10月30日までに行うことを掲げている。算定そのものは「第10期計画_サービス見込量の算定.xlsx」による。既定値（決着しない場合の扱い）によって算定しているため、ご決定をいただいた事項は10月30日の再算定で置き換わる</t>
+          <t>令和8年9月26日に提示した第1次概算の版。提示した時点の値を残すため、以後は作り直していない（算定を改めた後の値は「第10期計画_サービス見込量の算定.xlsx」による）。いま手元にある資料で算定できるところまで見込量を進めたもの。年報（令和7年度）の要介護度別の明細を収めたことにより、サービス種別×要介護度の実績が確定値で得られるようになったため、要介護度別に利用率を固定して延ばす算定に改めた。従前の一律の伸びとの差は月額＋8円である。利用回（日）数の見込み（法第117条第2項第1号）、地域支援事業の量の見込み（同項第2号）、中長期推計（令和17年度・令和22年度）の見込量・給付費、要介護度別の給付費、供給の制約（定員上限）と在宅への振替、報酬改定率の感度を新たに算定した。見える化システムの率の分母を実績値から逆算し、見込量の利用率の分母が認定者数であって第1号被保険者数ではないことを確かめた。地域密着型介護老人福祉施設入所者生活介護は令和11年度に定員の99.9％に達する。決着していない事項は過年度の数値を据え置き、何をどう置いたかを23件すべて掲げている。必要利用定員総数は現定員の据え置き案を掲げるにとどめ、計画素案の本文は［要協議］のまま残している。ご判断をお願いする事項6件、ご協議をお願いする事項1件、確認をお願いする事項3件、資料のご提供をお願いする事項1件を含む</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
+          <t>第10期計画_サービス見込量の算定_第2次概算.xlsx</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
+          <t>第2次概算（令和8年10月30日）の組立て。第1次概算（令和8年9月26日）からの差分、保険料算定表の記号A〜Jの対照、見込量・利用回（日）数・給付費の種別ごとの差分、中長期推計、月額を動かす前提、見える化システムの出力との対照、残る未決と既定値、10月30日までに行うことを掲げている。算定そのものは「第10期計画_サービス見込量の算定.xlsx」による。既定値（決着しない場合の扱い）によって算定しているため、ご決定をいただいた事項は10月30日の再算定で置き換わる</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1660,19 +1660,19 @@
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
+          <t>第10期計画_サービス見込量算定_統合報告書.xlsx</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
+          <t>サービス見込量の算定に関する4件の成果品（基準年度とパターンの比較、季節性の検証と施策反映の設計、対計画比の偏りの補正試算、趨勢に現れない要因の分析）を1件に束ねた統合報告書。全36シートを収録したうえで、算定の全体像と採用案、月額への効きの統合一覧（24件）、記載事項の網羅点検（26事項。対応5・一部対応12・未対応9）、論点漏れの是正の方針（7件）、成果品の統合候補（7群）を新たに加えた。介護保険法第117条第2項・第3項、社会福祉法等の一部を改正する法律（令和8年法律第51号）、国の第10期基本指針（案）の記載事項と突き合わせ、中長期推計が認定者数にとどまること、地域支援事業の量の見込みがないことなどを論点漏れとして特定した。ご判断をお願いする事項6件を含む</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1685,19 +1685,19 @@
       <c r="A41" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_ヒアリング前事前打合せ_確認事項.xlsx</t>
+          <t>第10期計画_チェック依頼_確認箇所と手順.docx</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月8日の事前打合せ（構成3町への町別ヒアリングの前に広域連合と受託者で行うもの）で用いる資料。打合せが1〜2時間であることを踏まえ、この場で決めるものをA群・B群・C群に分けて所要の目安を分で付した最低限の確認事項と時間配分（90分の案・120分の案）、仮置きによる算定の結果、事前にお決めいただきたい事項、ヒアリングで構成3町へ伺う事項（町別及び3町共通）と町からご提供をお願いする資料、保険料の月額を動かす前提、ヒアリングの進め方を1枚にまとめたもの。ヒアリングの場で用いる資料は「3町ヒアリング資料」及び「10月 地域課題の整理と3町協議の確認事項」による</t>
+          <t>この業務に携わっていない者が成果品を点検するための手引き（全10節・表10点）。点検を3層に分け、①スクリプトを再実行して自己点検の終了コードとdocx の検証を確かめる層、②数値の出所を辿る層、③記述の当否と守るべき制約を見る層の優先順で示している。件数・シート数・進捗・素案の規模・確認事項・算定値はいずれも実物又はソースから数えており、成果品を改訂すると追随する。出所により値が異なるもの5件、定員と読み違えやすい値4件、この業務で実際に起きた誤り8件を、気づいた経緯と手立てとともに掲げた。点検の記録様式と分担の案を含む。担当者名は記入枠としている</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1710,19 +1710,19 @@
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_レビュー対応記録.xlsx</t>
+          <t>第10期計画_ヒアリング前事前打合せ_確認事項.xlsx</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
+          <t>令和8年10月8日の事前打合せ（構成3町への町別ヒアリングの前に広域連合と受託者で行うもの）で用いる資料。打合せが1〜2時間であることを踏まえ、この場で決めるものをA群・B群・C群に分けて所要の目安を分で付した最低限の確認事項と時間配分（90分の案・120分の案）、仮置きによる算定の結果、事前にお決めいただきたい事項、ヒアリングで構成3町へ伺う事項（町別及び3町共通）と町からご提供をお願いする資料、保険料の月額を動かす前提、ヒアリングの進め方を1枚にまとめたもの。ヒアリングの場で用いる資料は「3町ヒアリング資料」及び「10月 地域課題の整理と3町協議の確認事項」による</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1735,19 +1735,19 @@
       <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_世帯構成の突合.xlsx</t>
+          <t>第10期計画_レビュー対応記録.xlsx</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>国勢調査・住民基本台帳との突合</t>
+          <t>受託者の点検対応の記録。ご決定を要する事項は「発注者確認事項一覧」に移してある</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
+          <t>第10期計画_世帯構成の突合.xlsx</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
+          <t>国勢調査・住民基本台帳との突合</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
+          <t>第10期計画_中間報告の根拠対照表.xlsx</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
+          <t>中間報告の記述と出典の対照。第三者検証用の索引</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1810,19 +1810,19 @@
       <c r="A46" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
+          <t>第10期計画_中間報告会議議事録_令和8年8月26日.odt</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
+          <t>第9期計画の評価・検証 中間報告の会議の議事録（校正反映後）</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果.xlsx</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
+          <t>受託者による校正の記録。8月工程に照らした網羅性の点検を含む</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
+          <t>第10期計画_中間報告会議議事録の校正結果_第2回.xlsx</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
+          <t>編集後の版に対する第2回の校正の記録。発注者による編集5件の評価と、本文に反映した3件・ご提案3件</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1885,19 +1885,19 @@
       <c r="A49" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_主張の根拠水準の棚卸しと再レビュー.xlsx</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>同上。主張ごとの根拠水準の自己点検。不足資料18件は「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
+          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価の取りまとめと第10期への反映.pdf</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>同左のPDF版。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
+          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価の取りまとめと第10期への反映.xlsx</t>
+          <t>第10期計画_交付金評価の取りまとめと第10期への反映.pdf</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>交付金の評価結果を推移・全国との比較・未得点項目の3つの側から取りまとめ、第10期計画への反映の可否を判定したもの。3町の得点は3か年ほぼ横ばいである一方、全国平均が32.5点上がったため全国での位置は下がっている。大項目別に改善14件・低下14件を掲げ、全国の多くの市町村が得点しているのに3町とも0点である明細列38件を17の大項目に束ねて、可4・条件付き12・現時点では不可1と判定した。構成3町のうち一部の町のみ得点している明細列78件は区域内で広げる余地がある。全国集計から広域連合・一部事務組合38団体と構成市町村205を割り出し、構成市町村の得点の平均で比べたところ、当連合は38団体中36位・町村のみで構成する11団体中10位・北海道内4団体の中で最も低い。19施策を介して計画素案の章節・10月の協議資料・確認事項と対にしている</t>
+          <t>同左のPDF版。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_交付金評価の取りまとめと第10期への反映.xlsx</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
+          <t>交付金の評価結果を推移・全国との比較・未得点項目の3つの側から取りまとめ、第10期計画への反映の可否を判定したもの。3町の得点は3か年ほぼ横ばいである一方、全国平均が32.5点上がったため全国での位置は下がっている。大項目別に改善14件・低下14件を掲げ、全国の多くの市町村が得点しているのに3町とも0点である明細列38件を17の大項目に束ねて、可4・条件付き12・現時点では不可1と判定した。構成3町のうち一部の町のみ得点している明細列78件は区域内で広げる余地がある。全国集計から広域連合・一部事務組合38団体と構成市町村205を割り出し、構成市町村の得点の平均で比べたところ、当連合は38団体中36位・町村のみで構成する11団体中10位・北海道内4団体の中で最も低い。19施策を介して計画素案の章節・10月の協議資料・確認事項と対にしている</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2035,19 +2035,19 @@
       <c r="A55" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2110,19 +2110,19 @@
       <c r="A58" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計コーホート分析の妥当性検証.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>社内の人口推計のファイル（令和8年10月1日・10月2日）を点検し、コーホート変化率法の組み方を検証したもの。式の点検7項目のうち3項目が不適合で、東川町だけ90歳以上の変化率の分母が5年前の90歳以上になっている（開放区間であるから5年前の85歳以上を分母とする）。この1点により東川町の総人口が令和32年度で実績の4.7倍へ発散する。95〜99歳・100歳以上に90歳以上の率を流用している点は3町に共通する。正しく組み直すと65歳以上（3町計）は横ばいとなり、当方の案Cと1.4〜4.9％以内で一致する。「令和5年推計を元にした補正」の女は男と全ての欄が同一であり女の値が入っていない。受領資料のスケジュールによりパブリックコメントの期間と令和9年2月以降の会議の日程が分かった（確認事項No.19）。修正の提案11件を優先度の順に掲げている</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護給付費分科会の論点整理の受領点検.xlsx</t>
+          <t>第10期計画_人口推計コーホート分析の妥当性検証.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>社会保障審議会介護給付費分科会（第256回から第270回）において令和9年度介護報酬改定に向けて検討されている論点31件を、計画素案・サービス見込量の算定・確認事項の台帳と突き合わせたもの。当区域に直結するものが17件あり、うち特に当区域の事情に関わるものとして短期入所生活介護の季節利用に係る例外（積雪期）、夜間対応型訪問介護の定期巡回への移行（移行猶予 令和11年3月）、高齢者向け住まいに係る通所介護等の報酬区分の見直し、特定地域における配置の弾力化、特別養護老人ホームの指定定員と実際の受入能力の差の5件を掲げている。国の公表の予定は、改定の考え方及び運営基準に関する整理が令和8年12月頃、諮問及び答申が令和9年1月頃であり、いずれも第2次概算（令和8年10月30日）より後である。検討されている事項はいずれも算定を止めるものではなく、量は令和7年度の実績により算定し、単価及び制度は現行制度で算定したうえで確定情報により再算定する。本整理に資料の原本は同梱されていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない（確認事項No.182）。原典による確認は別冊「介護給付費分科会資料（原典）の受領点検」による</t>
+          <t>社内の人口推計のファイル（令和8年10月1日・10月2日）を点検し、コーホート変化率法の組み方を検証したもの。式の点検7項目のうち3項目が不適合で、東川町だけ90歳以上の変化率の分母が5年前の90歳以上になっている（開放区間であるから5年前の85歳以上を分母とする）。この1点により東川町の総人口が令和32年度で実績の4.7倍へ発散する。95〜99歳・100歳以上に90歳以上の率を流用している点は3町に共通する。正しく組み直すと65歳以上（3町計）は横ばいとなり、当方の案Cと1.4〜4.9％以内で一致する。「令和5年推計を元にした補正」の女は男と全ての欄が同一であり女の値が入っていない。受領資料のスケジュールによりパブリックコメントの期間と令和9年2月以降の会議の日程が分かった（確認事項No.19）。修正の提案11件を優先度の順に掲げている</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx</t>
+          <t>第10期計画_介護給付費分科会の論点整理の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料25件（第262回 資料1から資料4、第263回 資料1から資料5、第264回 資料1から資料5、第268回 基本的な視点（案）、第269回 資料1から資料4、第270回 資料1から資料5。全1,037頁）を読み、当方の論点の整理と突き合わせたもの。論点7件を原典により確かめ、1件に是正を要することが分かり、整理にない21件が新たに分かった。是正したのは夜間対応型訪問介護の経過措置の期限であり、原典の中に令和11年度末までとするものと令和11年3月までとするものの2通りの記載がある。新たに分かったもののうち当区域に関わるものは、登録施設介護（予防）支援の施行日が令和9年4月1日ではないこと（公布の日から3年を超えない範囲内の政令で定める日）、地域区分の広域連合ルールと令和9年度改定における広域化の検討、同一建物等居住者へのサービス提供の実態、生産性向上推進のための協議会の設置が都道府県の義務となったこと、中山間地域に係る加算が3種類あること、短期入所療養介護への長期利用減算の新設、中山間地域等における入浴介助を目的とするサービスの特例、業務継続に係る市町村の助言等の状況である。計画素案は16箇所を改めた</t>
+          <t>社会保障審議会介護給付費分科会（第256回から第270回）において令和9年度介護報酬改定に向けて検討されている論点31件を、計画素案・サービス見込量の算定・確認事項の台帳と突き合わせたもの。当区域に直結するものが17件あり、うち特に当区域の事情に関わるものとして短期入所生活介護の季節利用に係る例外（積雪期）、夜間対応型訪問介護の定期巡回への移行（移行猶予 令和11年3月）、高齢者向け住まいに係る通所介護等の報酬区分の見直し、特定地域における配置の弾力化、特別養護老人ホームの指定定員と実際の受入能力の差の5件を掲げている。国の公表の予定は、改定の考え方及び運営基準に関する整理が令和8年12月頃、諮問及び答申が令和9年1月頃であり、いずれも第2次概算（令和8年10月30日）より後である。検討されている事項はいずれも算定を止めるものではなく、量は令和7年度の実績により算定し、単価及び制度は現行制度で算定したうえで確定情報により再算定する。本整理に資料の原本は同梱されていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない（確認事項No.182）。原典による確認は別冊「介護給付費分科会資料（原典）の受領点検」による</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2185,19 +2185,19 @@
       <c r="A61" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料25件（第262回 資料1から資料4、第263回 資料1から資料5、第264回 資料1から資料5、第268回 基本的な視点（案）、第269回 資料1から資料4、第270回 資料1から資料5。全1,037頁）を読み、当方の論点の整理と突き合わせたもの。論点7件を原典により確かめ、1件に是正を要することが分かり、整理にない21件が新たに分かった。是正したのは夜間対応型訪問介護の経過措置の期限であり、原典の中に令和11年度末までとするものと令和11年3月までとするものの2通りの記載がある。新たに分かったもののうち当区域に関わるものは、登録施設介護（予防）支援の施行日が令和9年4月1日ではないこと（公布の日から3年を超えない範囲内の政令で定める日）、地域区分の広域連合ルールと令和9年度改定における広域化の検討、同一建物等居住者へのサービス提供の実態、生産性向上推進のための協議会の設置が都道府県の義務となったこと、中山間地域に係る加算が3種類あること、短期入所療養介護への長期利用減算の新設、中山間地域等における入浴介助を目的とするサービスの特例、業務継続に係る市町村の助言等の状況である。計画素案は16箇所を改めた</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2235,19 +2235,19 @@
       <c r="A63" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2310,19 +2310,19 @@
       <c r="A66" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2360,19 +2360,19 @@
       <c r="A68" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2385,19 +2385,19 @@
       <c r="A69" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2435,19 +2435,19 @@
       <c r="A71" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_参照条文の受領点検.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月15日に受領した参照条文（社会福祉法等の一部を改正する法律案。全45頁・16法令）の文字起こしを読み、当方の整理と突き合わせたもの。原本は条文の部分が画像であって文字の層がなく読み取れなかったが、文字起こしのご提供により介護保険法第117条の項の全体（全14項）及び第3項の全10号、第118条並びに第115条の45の項及び号を確認した（確認事項No.181の解決）。従前の記述の誤りが5件分かった。うち重いものは、医療計画及び地域医療構想との整合性の確保は都道府県介護保険事業支援計画の義務（第118条第10項）であって市町村介護保険事業計画の義務ではないこと（市町村計画が整合性を確保すべき相手は地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項の市町村計画である）と、混合型及び介護専用型の特定施設入居者生活介護に係る必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（第118条第2項第1号・第4項）であって本計画の記載事項ではないこと（確認事項No.113の解決）の2件である。新たに分かったものは10件で、地域支援事業費に政令上の上限があること（第115条の45第4項）、介護老人保健施設の開設の許可に当たって北海道知事が本計画との調整を図る見地からの意見を求めなければならないこと（第94条第6項）を含む。文字起こしは未校正の光学文字認識によるものであるため、条、項及び号の番号を用い条文の文言は計画素案に引用しない。確からしさは新旧対照条文との突合6件により確かめている。収録されている介護保険法は医療法等の一部を改正する法律（令和7年法律第87号）による改正後の未施行の版である。</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表データ管理台帳.xlsx</t>
+          <t>第10期計画_参照条文の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
+          <t>令和8年10月15日に受領した参照条文（社会福祉法等の一部を改正する法律案。全45頁・16法令）の文字起こしを読み、当方の整理と突き合わせたもの。原本は条文の部分が画像であって文字の層がなく読み取れなかったが、文字起こしのご提供により介護保険法第117条の項の全体（全14項）及び第3項の全10号、第118条並びに第115条の45の項及び号を確認した（確認事項No.181の解決）。従前の記述の誤りが5件分かった。うち重いものは、医療計画及び地域医療構想との整合性の確保は都道府県介護保険事業支援計画の義務（第118条第10項）であって市町村介護保険事業計画の義務ではないこと（市町村計画が整合性を確保すべき相手は地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項の市町村計画である）と、混合型及び介護専用型の特定施設入居者生活介護に係る必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（第118条第2項第1号・第4項）であって本計画の記載事項ではないこと（確認事項No.113の解決）の2件である。新たに分かったものは10件で、地域支援事業費に政令上の上限があること（第115条の45第4項）、介護老人保健施設の開設の許可に当たって北海道知事が本計画との調整を図る見地からの意見を求めなければならないこと（第94条第6項）を含む。文字起こしは未校正の光学文字認識によるものであるため、条、項及び号の番号を用い条文の文言は計画素案に引用しない。確からしさは新旧対照条文との突合6件により確かめている。収録されている介護保険法は医療法等の一部を改正する法律（令和7年法律第87号）による改正後の未施行の版である。</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_図表データ管理台帳.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2660,19 +2660,19 @@
       <c r="A80" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2710,19 +2710,19 @@
       <c r="A82" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2835,19 +2835,19 @@
       <c r="A87" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2910,19 +2910,19 @@
       <c r="A90" s="6" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2985,19 +2985,19 @@
       <c r="A93" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_改正後の条文及び特定地域の受領点検.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月15日に受領した社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）、特定地域（中山間・人口減少地域）の考え方について（社会保障審議会介護保険部会 第135回 資料3）及び介護保険における3つの加算の対象地域一覧を読み、当方の整理と突き合わせたもの。従前は法律案要綱により整理していたため号及び項の一部を［要確認］としていたが、改正後の介護保険法第117条、第115条の48（支援会議）、第118条第2項及び第120条の3から第120条の5まで（協議会）の内容が確定した。中長期的な推計は、量が定めるものとされる事項（第2項第3号）、費用の額及び保険料の水準が定めるよう努めるものとされる事項（第3項第3号）であり義務の程度が異なる。あわせて、特別地域加算の対象地域に構成3町がいずれも掲げられていないこと（確認事項No.1の解決）と、北海道は全域が豪雪地帯であるため中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の地域の要件には該当することを確認した。計画素案15箇所を改めた。</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_改正後の条文及び特定地域の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>令和8年10月15日に受領した社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）、特定地域（中山間・人口減少地域）の考え方について（社会保障審議会介護保険部会 第135回 資料3）及び介護保険における3つの加算の対象地域一覧を読み、当方の整理と突き合わせたもの。従前は法律案要綱により整理していたため号及び項の一部を［要確認］としていたが、改正後の介護保険法第117条、第115条の48（支援会議）、第118条第2項及び第120条の3から第120条の5まで（協議会）の内容が確定した。中長期的な推計は、量が定めるものとされる事項（第2項第3号）、費用の額及び保険料の水準が定めるよう努めるものとされる事項（第3項第3号）であり義務の程度が異なる。あわせて、特別地域加算の対象地域に構成3町がいずれも掲げられていないこと（確認事項No.1の解決）と、北海道は全域が豪雪地帯であるため中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の地域の要件には該当することを確認した。計画素案15箇所を改めた。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3135,19 +3135,19 @@
       <c r="A99" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3185,19 +3185,19 @@
       <c r="A101" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認事項の資料徴求と公表資料による確認.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお待ちしている事項の一覧を、何をすれば決着するかという軸で区分したもの。A 広域連合（及び構成3町等）から資料の徴求を要するもの、B 公表資料により確認できるもの、B待 公表を待つもの（国の政令・省令・告示）、C ご判断・ご決定を求めるもの、D 資料の徴求を要しないものの5区分による。区分Aの全件に資料が届かない場合の扱いを付し、①安全側の置き方で算定する、②未確定箇所として残す、③当該の記載を掲げない、④現に確認できている値で確定するの4つに分けた。区分Aのうち大半は資料が届かなくても計画本文を確定でき、未確定箇所の記号が残るものは限られる。優先してご提供をお願いするものを、保険料の月額に効くもの、介護保険法第117条に関わるもの、影響度の高いもの及び資料が届かないと計画の記載に跡が残るものの4つの観点で掲げた。資料が届かない場合の扱いは受託者の仮置きであり決定ではない。</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_確認事項の資料徴求と公表資料による確認.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお待ちしている事項の一覧を、何をすれば決着するかという軸で区分したもの。A 広域連合（及び構成3町等）から資料の徴求を要するもの、B 公表資料により確認できるもの、B待 公表を待つもの（国の政令・省令・告示）、C ご判断・ご決定を求めるもの、D 資料の徴求を要しないものの5区分による。区分Aの全件に資料が届かない場合の扱いを付し、①安全側の置き方で算定する、②未確定箇所として残す、③当該の記載を掲げない、④現に確認できている値で確定するの4つに分けた。区分Aのうち大半は資料が届かなくても計画本文を確定でき、未確定箇所の記号が残るものは限られる。優先してご提供をお願いするものを、保険料の月額に効くもの、介護保険法第117条に関わるもの、影響度の高いもの及び資料が届かないと計画の記載に跡が残るものの4つの観点で掲げた。資料が届かない場合の扱いは受託者の仮置きであり決定ではない。</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3335,19 +3335,19 @@
       <c r="A107" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3435,19 +3435,19 @@
       <c r="A111" s="6" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3535,19 +3535,19 @@
       <c r="A115" s="6" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3635,19 +3635,19 @@
       <c r="A119" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3685,19 +3685,19 @@
       <c r="A121" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3760,19 +3760,19 @@
       <c r="A124" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。必要資料が未受領であることによる暫定値であり確定値ではない。その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。必要資料が未受領であることによる暫定値であり確定値ではない。その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3835,19 +3835,19 @@
       <c r="A127" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3860,19 +3860,19 @@
       <c r="A128" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3885,19 +3885,19 @@
       <c r="A129" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3910,19 +3910,19 @@
       <c r="A130" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3935,19 +3935,19 @@
       <c r="A131" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3960,19 +3960,19 @@
       <c r="A132" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3985,19 +3985,19 @@
       <c r="A133" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4010,19 +4010,19 @@
       <c r="A134" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4085,19 +4085,19 @@
       <c r="A137" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4110,19 +4110,19 @@
       <c r="A138" s="6" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4160,19 +4160,19 @@
       <c r="A140" s="6" t="n">
         <v>136</v>
       </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -4185,19 +4185,19 @@
       <c r="A141" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="B141" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4210,19 +4210,19 @@
       <c r="A142" s="6" t="n">
         <v>138</v>
       </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -4260,19 +4260,19 @@
       <c r="A144" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="B144" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -4292,129 +4292,154 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
+      <c r="D146" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="3" t="inlineStr">
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="28" customHeight="1">
-      <c r="A148" s="4" t="inlineStr">
+    <row r="149" ht="28" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr"/>
-      <c r="E148" s="4" t="inlineStr"/>
-    </row>
-    <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="n">
+      <c r="D149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr"/>
+    </row>
+    <row r="150" ht="26" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="C149" s="7" t="inlineStr">
+      <c r="C150" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D149" s="7" t="inlineStr"/>
-      <c r="E149" s="7" t="inlineStr"/>
-    </row>
-    <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C150" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr"/>
       <c r="E150" s="7" t="inlineStr"/>
     </row>
     <row r="151" ht="26" customHeight="1">
-      <c r="A151" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B151" s="6" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr"/>
       <c r="E151" s="7" t="inlineStr"/>
     </row>
     <row r="152" ht="26" customHeight="1">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B152" s="6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr"/>
       <c r="E152" s="7" t="inlineStr"/>
     </row>
     <row r="153" ht="26" customHeight="1">
-      <c r="A153" s="12" t="inlineStr">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr"/>
+      <c r="E153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154" ht="26" customHeight="1">
+      <c r="A154" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B153" s="13" t="n">
-        <v>141</v>
-      </c>
-      <c r="C153" s="14" t="inlineStr"/>
-      <c r="D153" s="14" t="inlineStr"/>
-      <c r="E153" s="14" t="inlineStr"/>
-    </row>
-    <row r="155" ht="76" customHeight="1">
-      <c r="A155" s="11" t="inlineStr">
+      <c r="B154" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="C154" s="14" t="inlineStr"/>
+      <c r="D154" s="14" t="inlineStr"/>
+      <c r="E154" s="14" t="inlineStr"/>
+    </row>
+    <row r="156" ht="76" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4424,8 +4449,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A147:E147"/>
-    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="A148:E148"/>
+    <mergeCell ref="A156:E156"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
+          <t>第10期計画_事業所ヒアリングを行わない場合の外部資料による確認.xlsx</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
+          <t>区域内の事業所への聴取を行わないことを前提として、公表されている資料によりどこまで確かめられるかを区分したもの。介護サービス情報公表システムにより、構成3町の事業所について定員・共同生活住居数・利用者数・入居率・総従業者数・職種別の従業者数と退職者数・経験年数の割合・離職率・空き人数・協力医療機関・家賃・介護報酬の加算の算定状況が公表されていることを確かめ、74行（47の事業所番号）を掲げた。施設・居住系の定員は北海道の名簿と一致し、認知症対応型共同生活介護は6事業所99人・共同生活住居11である。特定施設の定員は名簿156人・公表システム158人で差がある。確かめられないのは、整備又は事業の実施の意向、職員を確保できる見通し、受入れを制限しているかどうか、積雪期の利用の実態である。外部資料のホストは到達12・遮断3であり、追加で許可をお願いするものはない。見える化システムはホストへ到達できるが地方公共団体の職員のアカウントを要するため、事業所分析機能の出力のご提供をお願いする。出所は介護サービス情報公表システムであり、転載に当たり出所を明記している。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
+          <t>第10期計画_事業所調査の照会票と確定値管理表.xlsx</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
+          <t>事業所への照会票と確定値の管理表。3町との調整に用いる</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.pdf</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
+          <t>同左のPDF版（全21ページ）。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価の取りまとめと第10期への反映.pdf</t>
+          <t>第10期計画_交付金 市町村分評価指標と3町の評価.xlsx</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>同左のPDF版。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
+          <t>保険者機能強化推進交付金及び介護保険保険者努力支援交付金の市町村分の評価指標（大項目53件・明細列299件）の構造と配点に、構成3町の3か年の得点を対応させたもの。全国1,741市町村・北海道179市町村の平均との比較、3町とも0点でありながら全国では多くの市町村が得点している明細列38件を掲げている。評価は市町村単位で行われ、広域連合の行に得点はない</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価の取りまとめと第10期への反映.xlsx</t>
+          <t>第10期計画_交付金評価の取りまとめと第10期への反映.pdf</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>交付金の評価結果を推移・全国との比較・未得点項目の3つの側から取りまとめ、第10期計画への反映の可否を判定したもの。3町の得点は3か年ほぼ横ばいである一方、全国平均が32.5点上がったため全国での位置は下がっている。大項目別に改善14件・低下14件を掲げ、全国の多くの市町村が得点しているのに3町とも0点である明細列38件を17の大項目に束ねて、可4・条件付き12・現時点では不可1と判定した。構成3町のうち一部の町のみ得点している明細列78件は区域内で広げる余地がある。全国集計から広域連合・一部事務組合38団体と構成市町村205を割り出し、構成市町村の得点の平均で比べたところ、当連合は38団体中36位・町村のみで構成する11団体中10位・北海道内4団体の中で最も低い。19施策を介して計画素案の章節・10月の協議資料・確認事項と対にしている</t>
+          <t>同左のPDF版。表の見出し行を各ページに繰り返し、横向き・幅に合わせて印刷する</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
+          <t>第10期計画_交付金評価の取りまとめと第10期への反映.xlsx</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
+          <t>交付金の評価結果を推移・全国との比較・未得点項目の3つの側から取りまとめ、第10期計画への反映の可否を判定したもの。3町の得点は3か年ほぼ横ばいである一方、全国平均が32.5点上がったため全国での位置は下がっている。大項目別に改善14件・低下14件を掲げ、全国の多くの市町村が得点しているのに3町とも0点である明細列38件を17の大項目に束ねて、可4・条件付き12・現時点では不可1と判定した。構成3町のうち一部の町のみ得点している明細列78件は区域内で広げる余地がある。全国集計から広域連合・一部事務組合38団体と構成市町村205を割り出し、構成市町村の得点の平均で比べたところ、当連合は38団体中36位・町村のみで構成する11団体中10位・北海道内4団体の中で最も低い。19施策を介して計画素案の章節・10月の協議資料・確認事項と対にしている</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2060,19 +2060,19 @@
       <c r="A56" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
+          <t>第10期計画_交付金評価指標と全国集計の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
+          <t>交付金の全国集計結果（令和6〜8年度）の原本と令和8年度評価指標の受領点検。収録値198値の突合、配点の検証、全国・北海道との3か年比較、成果指向型配分枠の新設。全国の個票は収録していない。令和8年9月25日に受領した都道府県分2件（評価指標38頁・全国集計（都道府県））の点検を加えた。都道府県分は市町村分とは別の評価であり、当広域連合及び構成3町の得点は載っていない。北海道は令和8年度550点・全国19位（前年度570点・10位）で、管内市町村の状況で決まる2項目が0点である。「著しく得点の低い市町村」の閾値は279.7点であり、構成3町（東川315・美瑛308・東神楽379）はいずれも該当しない。集計対象の市町村数は3か年とも1,741である</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
+          <t>第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
+          <t>人口推計の基礎を地方創生総合戦略とするご指示への対応。総合戦略の目標人口の制約3件、案Cの組立て、3案の比較、保険料への影響（概算 案A 6,670円・案B 6,578円・案C 6,774円、通し再計算による案C 6,740円）、確定を要する事項8件。採用案のご確認を要する</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
+          <t>第10期計画_人口推計の基礎の検証.xlsx</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
+          <t>推計の基礎に何を用いるかの検討。受託者の推奨を含む</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2135,19 +2135,19 @@
       <c r="A59" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_人口推計コーホート分析の妥当性検証.xlsx</t>
+          <t>第10期計画_人口推計の補正_65歳以上75歳以上の突合.xlsx</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>社内の人口推計のファイル（令和8年10月1日・10月2日）を点検し、コーホート変化率法の組み方を検証したもの。式の点検7項目のうち3項目が不適合で、東川町だけ90歳以上の変化率の分母が5年前の90歳以上になっている（開放区間であるから5年前の85歳以上を分母とする）。この1点により東川町の総人口が令和32年度で実績の4.7倍へ発散する。95〜99歳・100歳以上に90歳以上の率を流用している点は3町に共通する。正しく組み直すと65歳以上（3町計）は横ばいとなり、当方の案Cと1.4〜4.9％以内で一致する。「令和5年推計を元にした補正」の女は男と全ての欄が同一であり女の値が入っていない。受領資料のスケジュールによりパブリックコメントの期間と令和9年2月以降の会議の日程が分かった（確認事項No.19）。修正の提案11件を優先度の順に掲げている</t>
+          <t>住民基本台帳7年分との突合。補正率の採否のご判断を要する</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2160,19 +2160,19 @@
       <c r="A60" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護給付費分科会の論点整理の受領点検.xlsx</t>
+          <t>第10期計画_人口推計コーホート分析の妥当性検証.xlsx</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>社会保障審議会介護給付費分科会（第256回から第270回）において令和9年度介護報酬改定に向けて検討されている論点31件を、計画素案・サービス見込量の算定・確認事項の台帳と突き合わせたもの。当区域に直結するものが17件あり、うち特に当区域の事情に関わるものとして短期入所生活介護の季節利用に係る例外（積雪期）、夜間対応型訪問介護の定期巡回への移行（移行猶予 令和11年3月）、高齢者向け住まいに係る通所介護等の報酬区分の見直し、特定地域における配置の弾力化、特別養護老人ホームの指定定員と実際の受入能力の差の5件を掲げている。国の公表の予定は、改定の考え方及び運営基準に関する整理が令和8年12月頃、諮問及び答申が令和9年1月頃であり、いずれも第2次概算（令和8年10月30日）より後である。検討されている事項はいずれも算定を止めるものではなく、量は令和7年度の実績により算定し、単価及び制度は現行制度で算定したうえで確定情報により再算定する。本整理に資料の原本は同梱されていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない（確認事項No.182）。原典による確認は別冊「介護給付費分科会資料（原典）の受領点検」による</t>
+          <t>社内の人口推計のファイル（令和8年10月1日・10月2日）を点検し、コーホート変化率法の組み方を検証したもの。式の点検7項目のうち3項目が不適合で、東川町だけ90歳以上の変化率の分母が5年前の90歳以上になっている（開放区間であるから5年前の85歳以上を分母とする）。この1点により東川町の総人口が令和32年度で実績の4.7倍へ発散する。95〜99歳・100歳以上に90歳以上の率を流用している点は3町に共通する。正しく組み直すと65歳以上（3町計）は横ばいとなり、当方の案Cと1.4〜4.9％以内で一致する。「令和5年推計を元にした補正」の女は男と全ての欄が同一であり女の値が入っていない。受領資料のスケジュールによりパブリックコメントの期間と令和9年2月以降の会議の日程が分かった（確認事項No.19）。修正の提案11件を優先度の順に掲げている</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx</t>
+          <t>第10期計画_介護給付費分科会の論点整理の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料25件（第262回 資料1から資料4、第263回 資料1から資料5、第264回 資料1から資料5、第268回 基本的な視点（案）、第269回 資料1から資料4、第270回 資料1から資料5。全1,037頁）を読み、当方の論点の整理と突き合わせたもの。論点7件を原典により確かめ、1件に是正を要することが分かり、整理にない21件が新たに分かった。是正したのは夜間対応型訪問介護の経過措置の期限であり、原典の中に令和11年度末までとするものと令和11年3月までとするものの2通りの記載がある。新たに分かったもののうち当区域に関わるものは、登録施設介護（予防）支援の施行日が令和9年4月1日ではないこと（公布の日から3年を超えない範囲内の政令で定める日）、地域区分の広域連合ルールと令和9年度改定における広域化の検討、同一建物等居住者へのサービス提供の実態、生産性向上推進のための協議会の設置が都道府県の義務となったこと、中山間地域に係る加算が3種類あること、短期入所療養介護への長期利用減算の新設、中山間地域等における入浴介助を目的とするサービスの特例、業務継続に係る市町村の助言等の状況である。計画素案は16箇所を改めた</t>
+          <t>社会保障審議会介護給付費分科会（第256回から第270回）において令和9年度介護報酬改定に向けて検討されている論点31件を、計画素案・サービス見込量の算定・確認事項の台帳と突き合わせたもの。当区域に直結するものが17件あり、うち特に当区域の事情に関わるものとして短期入所生活介護の季節利用に係る例外（積雪期）、夜間対応型訪問介護の定期巡回への移行（移行猶予 令和11年3月）、高齢者向け住まいに係る通所介護等の報酬区分の見直し、特定地域における配置の弾力化、特別養護老人ホームの指定定員と実際の受入能力の差の5件を掲げている。国の公表の予定は、改定の考え方及び運営基準に関する整理が令和8年12月頃、諮問及び答申が令和9年1月頃であり、いずれも第2次概算（令和8年10月30日）より後である。検討されている事項はいずれも算定を止めるものではなく、量は令和7年度の実績により算定し、単価及び制度は現行制度で算定したうえで確定情報により再算定する。本整理に資料の原本は同梱されていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない（確認事項No.182）。原典による確認は別冊「介護給付費分科会資料（原典）の受領点検」による</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2210,19 +2210,19 @@
       <c r="A62" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
+          <t>第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
+          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料25件（第262回 資料1から資料4、第263回 資料1から資料5、第264回 資料1から資料5、第268回 基本的な視点（案）、第269回 資料1から資料4、第270回 資料1から資料5。全1,037頁）を読み、当方の論点の整理と突き合わせたもの。論点7件を原典により確かめ、1件に是正を要することが分かり、整理にない21件が新たに分かった。是正したのは夜間対応型訪問介護の経過措置の期限であり、原典の中に令和11年度末までとするものと令和11年3月までとするものの2通りの記載がある。新たに分かったもののうち当区域に関わるものは、登録施設介護（予防）支援の施行日が令和9年4月1日ではないこと（公布の日から3年を超えない範囲内の政令で定める日）、地域区分の広域連合ルールと令和9年度改定における広域化の検討、同一建物等居住者へのサービス提供の実態、生産性向上推進のための協議会の設置が都道府県の義務となったこと、中山間地域に係る加算が3種類あること、短期入所療養介護への長期利用減算の新設、中山間地域等における入浴介助を目的とするサービスの特例、業務継続に係る市町村の助言等の状況である。計画素案は16箇所を改めた</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
+          <t>第10期計画_介護高齢者福祉サービスガイド_構成案.docx</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
+          <t>富良野市のサービスガイドと同じ構成による当区域の構成案。介護保険の手続・費用と区域内74事業所の一覧は原案を作成済み。3町の高齢者福祉サービスと事業所の連絡先は記入枠。3町への照会を要する</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2260,19 +2260,19 @@
       <c r="A64" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
+          <t>第10期計画_代表KPIの振替案と確認事項の精査.xlsx</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
+          <t>代表KPIの振替の案と確認事項。ご協議を要する</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
+          <t>第10期計画_令和6年度決算書の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
+          <t>令和6年度決算書（介護保険特別会計）の受領点検。款項別の決算額、介護給付費準備基金の推移、年報の様式4との対照22項目</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
+          <t>第10期計画_令和8年8月28日受領資料の点検結果.xlsx</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
+          <t>令和8年8月28日受領の9件の点検結果。交付金評価の3町別・3か年、要介護認定の状況、成果品への反映箇所</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2335,19 +2335,19 @@
       <c r="A67" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
+          <t>第10期計画_住まいと施設の公表名簿との突合.xlsx</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
+          <t>公表情報との突合。管理者名・連絡先は収録していない</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
+          <t>第10期計画_保険料と施策評価の他団体比較.xlsx</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>所得段階の設定に関する検討。試算を含む</t>
+          <t>他団体との比較。比較対象の選び方は受託者の整理による</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2385,19 +2385,19 @@
       <c r="A69" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
+          <t>第10期計画_保険料の所得段階と低所得者軽減の検証.xlsx</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>所得段階の設定に関する検討。試算を含む</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2410,19 +2410,19 @@
       <c r="A70" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
+          <t>第10期計画_入力前段支援アプリの点検.xlsx</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
+          <t>弊社内の全国共通版（提出資料一覧・入力前段支援アプリ・運用ガイド）を本件の算定と突き合わせた点検の記録。算定式の骨格は当方と同じであり、差は受給率の分母の粒度（要介護度7区分か要介護・要支援の2区分か）だけである。第10期3か年で月額3円、令和22年度で0.22％。アプリの保険料の式に当方の値を入れると保険料収納必要額と円単位で一致する。見える化システムの画面の伸びの選択肢は4件で、アプリの候補と文言が一致しない。入力の落とし穴7件を掲げている。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
+          <t>第10期計画_内部確認結果への対応整理.xlsx</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
+          <t>広域連合の内部確認結果（令和8年9月3日）への対応整理。決定7の推奨案とその理由、代表KPI16項目及び改善事項8項目の再整理案（いずれも受託者案）、構成3町への確認事項8件、新たに生じた確認事項6件を含む</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2460,19 +2460,19 @@
       <c r="A72" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_参照条文の受領点検.xlsx</t>
+          <t>第10期計画_利用状況統計表（R8.8月審査分）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月15日に受領した参照条文（社会福祉法等の一部を改正する法律案。全45頁・16法令）の文字起こしを読み、当方の整理と突き合わせたもの。原本は条文の部分が画像であって文字の層がなく読み取れなかったが、文字起こしのご提供により介護保険法第117条の項の全体（全14項）及び第3項の全10号、第118条並びに第115条の45の項及び号を確認した（確認事項No.181の解決）。従前の記述の誤りが5件分かった。うち重いものは、医療計画及び地域医療構想との整合性の確保は都道府県介護保険事業支援計画の義務（第118条第10項）であって市町村介護保険事業計画の義務ではないこと（市町村計画が整合性を確保すべき相手は地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項の市町村計画である）と、混合型及び介護専用型の特定施設入居者生活介護に係る必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（第118条第2項第1号・第4項）であって本計画の記載事項ではないこと（確認事項No.113の解決）の2件である。新たに分かったものは10件で、地域支援事業費に政令上の上限があること（第115条の45第4項）、介護老人保健施設の開設の許可に当たって北海道知事が本計画との調整を図る見地からの意見を求めなければならないこと（第94条第6項）を含む。文字起こしは未校正の光学文字認識によるものであるため、条、項及び号の番号を用い条文の文言は計画素案に引用しない。確からしさは新旧対照条文との突合6件により確かめている。収録されている介護保険法は医療法等の一部を改正する法律（令和7年法律第87号）による改正後の未施行の版である。</t>
+          <t>令和8年8月審査分 介護保険 利用状況統計表（3町・各9頁）の受領点検。審査月単位・町別・サービス種類別・要介護度別の利用実人員・回数・単位数・費用総額・介護給付費を確認した。費用総額288,036,749円・介護給付費258,821,513円。要介護度別の和と小計の一致、町別・要介護度別の構成比、訪問系サービスの明細との突合により読み取りを確かめている。画像の写しであるため36か所を画像で確かめて是正した。訪問系の明細は氏名・年齢・被保険者番号を含むため格納せず集計値のみを収録している</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2485,19 +2485,19 @@
       <c r="A73" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表データ管理台帳.xlsx</t>
+          <t>第10期計画_参照条文の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
+          <t>令和8年10月15日に受領した参照条文（社会福祉法等の一部を改正する法律案。全45頁・16法令）の文字起こしを読み、当方の整理と突き合わせたもの。原本は条文の部分が画像であって文字の層がなく読み取れなかったが、文字起こしのご提供により介護保険法第117条の項の全体（全14項）及び第3項の全10号、第118条並びに第115条の45の項及び号を確認した（確認事項No.181の解決）。従前の記述の誤りが5件分かった。うち重いものは、医療計画及び地域医療構想との整合性の確保は都道府県介護保険事業支援計画の義務（第118条第10項）であって市町村介護保険事業計画の義務ではないこと（市町村計画が整合性を確保すべき相手は地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項の市町村計画である）と、混合型及び介護専用型の特定施設入居者生活介護に係る必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（第118条第2項第1号・第4項）であって本計画の記載事項ではないこと（確認事項No.113の解決）の2件である。新たに分かったものは10件で、地域支援事業費に政令上の上限があること（第115条の45第4項）、介護老人保健施設の開設の許可に当たって北海道知事が本計画との調整を図る見地からの意見を求めなければならないこと（第94条第6項）を含む。文字起こしは未校正の光学文字認識によるものであるため、条、項及び号の番号を用い条文の文言は計画素案に引用しない。確からしさは新旧対照条文との突合6件により確かめている。収録されている介護保険法は医療法等の一部を改正する法律（令和7年法律第87号）による改正後の未施行の版である。</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2510,19 +2510,19 @@
       <c r="A74" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_図表集_白黒.xlsx</t>
+          <t>第10期計画_図表データ管理台帳.xlsx</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>図表の実体。出典と基準日を各シートに付している</t>
+          <t>計画本文に差し込む図の数値をエクセルの上で管理する台帳。図1点につき1枚のデータシートを設け、数値のセルとネイティブグラフを結び付けている。数値を直すとシート上のグラフがその場で変わり、作図を実行し直せば計画本文の図も同じ値になる。あわせて、別冊の図表集のグラフと数値を機械で突き合わせた結果、保険者機能強化推進交付金等の評価が求める分析と図表の対応、新たに作る図表の候補、計画素案 資料7の図表番号一覧との突合を収めた</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2535,19 +2535,19 @@
       <c r="A75" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
+          <t>第10期計画_図表集_白黒.xlsx</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
+          <t>図表の実体。出典と基準日を各シートに付している</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2560,19 +2560,19 @@
       <c r="A76" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
+          <t>第10期計画_地域ケア会議_受領点検とKPI設計案.xlsx</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
+          <t>令和8年9月11日に受領した地域ケア会議に関する資料5件（PDF82ファイル）の受領点検と、第9期施策2-5「地域ケア会議の推進」のKPI設計案。5件のうち3件は厚生労働省の原典であり出典として引用できる。2件には転載を禁ずる旨の記載があり、出典として参照するにとどめる又は比較材料としてのみ用いる整理とした。個人情報を含む資料2件は保管していない。KPIは市町村マニュアルが示す構造・過程・結果の3視点により13指標を並べ、代表KPIを施策化への転換率とする案とした。記録様式の項目案12件と集計の様式10件を併せて示している。ご判断をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2585,19 +2585,19 @@
       <c r="A77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
+          <t>第10期計画_地域分析・検討シート_記載案.xlsx</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
+          <t>地域包括ケア「見える化」システムの地域分析・検討シート（令和8年9月30日受領）の記入欄15件（3群×5欄。全国平均等との比較・乖離の考察（仮説の設定）・設定した仮説の確認・検証方法・問題を解決するための対応策・自由記述）に記載する内容の案。全9シート。受領した時点では15欄がいずれも空欄であり、比較地域も未設定である。指標39件の自地域・北海道平均・全国平均の対比（全国平均を上回る6件・下回る9件）、仮説の裏づけとなる数値と出所19件、検証に要する資料12件（優先A5件）を掲げた。主たる比較は12か月分の令和7年度による（令和8年度は年度の途中の値である）。様式の令和7年度の値は当広域連合が年報から算定した値と一致する（1人あたり利用日数・回数9区分・認定率）。様式への記載は構成3町との協議を経て確定する</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_地域差の分析.xlsx</t>
+          <t>第10期計画_地域密着型サービス基準省令の論点整理.xlsx</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
+          <t>令和8年9月10日にご提示のあった指定地域密着型サービスの事業の人員、設備及び運営に関する基準（平成18年厚生労働省令第34号）の全文を、当区域の実データと突き合わせて論点を整理した協議資料。連携型定期巡回、共用型認知症対応型通所介護、過疎地域における小規模多機能型居宅介護の定員超過の特例、サテライト型、令和9年4月から義務となる2件など14件。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項6件と、資料のご提供をお願いする事項5件を含む</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_基金条例の確認.xlsx</t>
+          <t>第10期計画_地域差の分析.xlsx</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
+          <t>自給率・給付水準の地域差。見える化δは取扱い注意の記載がある</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_妥当性検証報告書.xlsx</t>
+          <t>第10期計画_基金条例の確認.xlsx</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
+          <t>基金条例の確認。基金の正式名称、取崩しの要件、積立ての上限（保険料収納必要額の100分の10）。上限の読み方と第10期の取崩方針についてご協議を要する</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2685,19 +2685,19 @@
       <c r="A81" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
+          <t>第10期計画_妥当性検証報告書.xlsx</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>受領した調査データの点検記録</t>
+          <t>検証結果に受託者の判断による判定を含む。各シートに根拠と留保を併記している</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_実施済み調査_結果報告書.docx</t>
+          <t>第10期計画_実施済み3調査の受領点検と集計.xlsx</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>実施済み調査の結果報告</t>
+          <t>受領した調査データの点検記録</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2735,19 +2735,19 @@
       <c r="A83" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
+          <t>第10期計画_実施済み調査_結果報告書.docx</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
+          <t>実施済み調査の結果報告</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
+          <t>第10期計画_対計画比の偏りの補正試算.xlsx</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>推計値。補正の採否について発注者のご判断を要する</t>
+          <t>サービス別の対計画比の偏りを補正した場合の見込量と保険料の試算。第7期から第9期までの8年度の対計画比はサービス別に34.0％から146.6％まで開き、全体は8年度すべてで100％未満である。見込量の伸びを一律（認定者数の伸び）からサービス別の趨勢を半分反映する置き方に改める案を、バックテスト（起点と予測年数を変えた5通り・30設定）で選んだ。施設・居住系を減らすかどうかで月額の符号が変わる。ご判断をお願いする事項3件と、確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
+          <t>第10期計画_将来推計_人口と認定者数.xlsx</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>推計値。単価等が未確定のため仮置きを含む</t>
+          <t>推計値。補正の採否について発注者のご判断を要する</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
+          <t>第10期計画_将来推計_第2段階_サービス見込量.xlsx</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
+          <t>推計値。単価等が未確定のため仮置きを含む</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
+          <t>第10期計画_将来推計_第3段階_給付費と保険料.xlsx</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
+          <t>将来推計 第3段階（給付費と保険料）の暫定算定。標準給付費見込額から保険料基準額までの組立て、感度分析8件、基金の取崩シナリオ5件、所得段階別の月額。確定を要する事項9件を含み、確定値ではない</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2860,19 +2860,19 @@
       <c r="A88" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_年報月報の受領点検.xlsx</t>
+          <t>第10期計画_将来推計_需要3シナリオの感度表.xlsx</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
+          <t>3シナリオの試算。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -2885,19 +2885,19 @@
       <c r="A89" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
+          <t>第10期計画_年報月報の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
+          <t>介護保険事業状況報告の年報（令和6・7年度）・月報（令和8年4〜7月）の受領点検。介護給付費準備基金の残高、特別会計の決算額、保険料収納率、所得段階別被保険者数、代表KPIの独立した裏づけ</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
+          <t>第10期計画_広域連合において行うべき事業の優先順位.xlsx</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
+          <t>広域連合において行うべき事業20件の優先順位。富良野市のサービスガイドと鹿児島県の取組事例集を参照し、義務・欠落・実行・効果・主体の5項目で採点した。優先度A4件・B7件・C9件。優先順位は受託者の案であり決定を要する</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -2935,19 +2935,19 @@
       <c r="A91" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_必要事項の一覧.xlsx</t>
+          <t>第10期計画_従業員数の重複計上の整理.xlsx</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>不足資料・確認事項の一覧</t>
+          <t>社会資源一覧の従業員数の重複計上の整理。重複の候補8組と数え方の3案。ご確認欄を設けている</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -2960,19 +2960,19 @@
       <c r="A92" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品の送付区分表.xlsx</t>
+          <t>第10期計画_必要事項の一覧.xlsx</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
+          <t>不足資料・確認事項の一覧</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_成果品一覧.xlsx</t>
+          <t>第10期計画_成果品の送付区分表.xlsx</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
+          <t>送付区分の判断基準と、用いない表現の一覧。用いない表現を列挙する性質上、送付資料としては用いない</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3010,19 +3010,19 @@
       <c r="A94" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
+          <t>第10期計画_成果品一覧.xlsx</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
+          <t>内部保管資料を含む全成果品の一覧。送付時は「送付資料一覧」を用いる</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3035,19 +3035,19 @@
       <c r="A95" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_改正後の条文及び特定地域の受領点検.xlsx</t>
+          <t>第10期計画_所得段階別第1号被保険者数の将来推計.xlsx</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月15日に受領した社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）、特定地域（中山間・人口減少地域）の考え方について（社会保障審議会介護保険部会 第135回 資料3）及び介護保険における3つの加算の対象地域一覧を読み、当方の整理と突き合わせたもの。従前は法律案要綱により整理していたため号及び項の一部を［要確認］としていたが、改正後の介護保険法第117条、第115条の48（支援会議）、第118条第2項及び第120条の3から第120条の5まで（協議会）の内容が確定した。中長期的な推計は、量が定めるものとされる事項（第2項第3号）、費用の額及び保険料の水準が定めるよう努めるものとされる事項（第3項第3号）であり義務の程度が異なる。あわせて、特別地域加算の対象地域に構成3町がいずれも掲げられていないこと（確認事項No.1の解決）と、北海道は全域が豪雪地帯であるため中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の地域の要件には該当することを確認した。計画素案15箇所を改めた。</t>
+          <t>所得段階別第1号被保険者数の将来推計（確認事項No.156）。見える化システムの「保険料額の算定」画面が求める令和9・10・11・12・17・22・27・32年度の8年度について、16段階別の第1号被保険者数を算定した。実績の構成比を固定し、将来の第1号被保険者数（案C）に乗じている。整数化は最大剰余法により合計を保ち、各年度の合計は第1号被保険者数と一致する。構成比は令和6年度の実績で置いた。当方の保険料算定が採用している係数（0.991352）と同じであり、本表の人数から見える化システムが算定する補正後被保険者数が当方の値と一致するためである。構成比を令和7年度に改めると係数は1.015890となり算定上の月額が163円下がるが、これは本表の作り方ではなく係数の選択そのものである。当連合の所得段階は第9期の条例により16段階であり、見える化システムの標準（13段階）と異なるため、入力画面では所得段階の設定を弾力化とする。第10期の段階数・乗率は政令改正により変わり得るため暫定値である。本表の人数で算定し直した月額は当方の値と0.57円の差で一致する</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3060,19 +3060,19 @@
       <c r="A96" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_施策体系新旧対照表.xlsx</t>
+          <t>第10期計画_改正後の条文及び特定地域の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>第9期と第10期の対照。第10期側は案である</t>
+          <t>令和8年10月15日に受領した社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）、特定地域（中山間・人口減少地域）の考え方について（社会保障審議会介護保険部会 第135回 資料3）及び介護保険における3つの加算の対象地域一覧を読み、当方の整理と突き合わせたもの。従前は法律案要綱により整理していたため号及び項の一部を［要確認］としていたが、改正後の介護保険法第117条、第115条の48（支援会議）、第118条第2項及び第120条の3から第120条の5まで（協議会）の内容が確定した。中長期的な推計は、量が定めるものとされる事項（第2項第3号）、費用の額及び保険料の水準が定めるよう努めるものとされる事項（第3項第3号）であり義務の程度が異なる。あわせて、特別地域加算の対象地域に構成3町がいずれも掲げられていないこと（確認事項No.1の解決）と、北海道は全域が豪雪地帯であるため中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の地域の要件には該当することを確認した。計画素案15箇所を改めた。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3085,19 +3085,19 @@
       <c r="A97" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
+          <t>第10期計画_施策体系新旧対照表.xlsx</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
+          <t>第9期と第10期の対照。第10期側は案である</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3110,19 +3110,19 @@
       <c r="A98" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務工程管理表.xlsx</t>
+          <t>第10期計画_日次の状況と翌日の作業順位.xlsx</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の月別工程に対する進捗の管理表</t>
+          <t>1日の終わりに、WBS（業務内容別の進捗）の現況、ペンディング（決定待ち・資料待ち）の棚卸しと優先順位、決定を待たずに進められる作業、翌日の作業順位を1枚にしたもの。全7シート。基準日は実行した日とする。確認事項は業務工程管理表（正の台帳）から、据え置きと月額への効きは見込量算定から読むため、台帳を二重に持たない。優先順位は期限・止めている成果物・月額への効き・法定記載事項・決着しない場合の扱いの有無の5つで点を付けており、付け方は03シートに全て掲げている。機械で付けた順位であり、会議の日程・相手のご都合・作業の段取りは入っていないため人が並べ替えてよい。進捗の記録の基準日が当日でないと自己点検が不適合になり、WBSを更新しないと作れない。自己点検14件。業務の管理に用いるものであり、発注者への送付は想定しない</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
+          <t>第10期計画_業務工程管理表.xlsx</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
+          <t>仕様書５の月別工程に対する進捗の管理表</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3160,19 +3160,19 @@
       <c r="A100" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_概要版の構成案.xlsx</t>
+          <t>第10期計画_業務進捗報告書_令和8年8月分.docx</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
+          <t>仕様書４（1）〜（12）の区分ごとの月次進捗報告</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
+          <t>第10期計画_概要版の構成案.xlsx</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
+          <t>3案の比較と推奨。いずれを採るかは発注者のご判断による</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3210,19 +3210,19 @@
       <c r="A102" s="6" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_町別データシート.xlsx</t>
+          <t>第10期計画_構成町の意見への回答と工程の前倒し案.docx</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
+          <t>構成3町のご意見（令和8年9月9日共有）への回答。現状分析の共有時期、意見交換会の実施方法、サービス見込量の提示時期の3件はいずれも対応できる。第1次概算として構成町の一般会計繰入金の概算を示している。確定値ではない。ご判断をお願いする事項7件を含む</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3235,19 +3235,19 @@
       <c r="A103" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_発注者確認事項一覧.xlsx</t>
+          <t>第10期計画_町別データシート.xlsx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
+          <t>現状分析・地域課題の整理から町別の数値を抜き出したもの。構成町の高齢者福祉計画の作成にお使いいただくことを想定している。サービス見込量・給付費・保険料は保険者単位で算定するため町別には掲げていない（05シート）。出典から独立に再計算した点検の結果を06シートに収めている。町別の将来人口と世帯は見える化システムA系列（令和8年9月10日受領）による</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3260,19 +3260,19 @@
       <c r="A104" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認事項の資料徴求と公表資料による確認.xlsx</t>
+          <t>第10期計画_発注者確認事項一覧.xlsx</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>ご決定・ご確認をお待ちしている事項の一覧を、何をすれば決着するかという軸で区分したもの。A 広域連合（及び構成3町等）から資料の徴求を要するもの、B 公表資料により確認できるもの、B待 公表を待つもの（国の政令・省令・告示）、C ご判断・ご決定を求めるもの、D 資料の徴求を要しないものの5区分による。区分Aの全件に資料が届かない場合の扱いを付し、①安全側の置き方で算定する、②未確定箇所として残す、③当該の記載を掲げない、④現に確認できている値で確定するの4つに分けた。区分Aのうち大半は資料が届かなくても計画本文を確定でき、未確定箇所の記号が残るものは限られる。優先してご提供をお願いするものを、保険料の月額に効くもの、介護保険法第117条に関わるもの、影響度の高いもの及び資料が届かないと計画の記載に跡が残るものの4つの観点で掲げた。資料が届かない場合の扱いは受託者の仮置きであり決定ではない。</t>
+          <t>ご決定・ご確認をお願いする事項12件。受託者の推奨案を含む</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_確認依頼書.docx</t>
+          <t>第10期計画_確認事項の資料徴求と公表資料による確認.xlsx</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>確認をお願いする事項の依頼書</t>
+          <t>ご決定・ご確認をお待ちしている事項の一覧を、何をすれば決着するかという軸で区分したもの。A 広域連合（及び構成3町等）から資料の徴求を要するもの、B 公表資料により確認できるもの、B待 公表を待つもの（国の政令・省令・告示）、C ご判断・ご決定を求めるもの、D 資料の徴求を要しないものの5区分による。区分Aの全件に資料が届かない場合の扱いを付し、①安全側の置き方で算定する、②未確定箇所として残す、③当該の記載を掲げない、④現に確認できている値で確定するの4つに分けた。区分Aのうち大半は資料が届かなくても計画本文を確定でき、未確定箇所の記号が残るものは限られる。優先してご提供をお願いするものを、保険料の月額に効くもの、介護保険法第117条に関わるもの、影響度の高いもの及び資料が届かないと計画の記載に跡が残るものの4つの観点で掲げた。資料が届かない場合の扱いは受託者の仮置きであり決定ではない。</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
+          <t>第10期計画_確認依頼書.docx</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
+          <t>確認をお願いする事項の依頼書</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
+          <t>第10期計画_社人研推計の町別データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
+          <t>社人研「日本の地域別将来推計人口」（令和5年推計）結果表3-1〜3-4の受領点検。町別75歳以上を按分値から公表値に置き換えた結果と、町別の補正方向の変化4件、上川管内23団体との比較</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3360,19 +3360,19 @@
       <c r="A108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
+          <t>第10期計画_社会福祉法等改正法の法律案要綱の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
+          <t>令和8年10月14日に受領した社会福祉法等の一部を改正する法律案要綱（全31頁）及び令和5年改正の概要（1頁）を読み、当方の整理と突き合わせたもの。従前は部会資料（概要）により整理していたため施行期日の例外を2件しか把握していなかったが、要綱 第10の1により4区分が確定した。介護保険法の改正事項16件のうち11件に記述の是正を要することが分かり、14件が新たに分かった。当区域に関わるものは、介護支援専門員の資格に係る更新制の廃止が公布の日から1年6月を超えない範囲内の政令で定める日であり事業者に氏名の報告及び研修の受講の機会の確保の義務が生ずること、特定地域居宅サービス等事業の対象が6区分であり費用負担が介護予防・日常生活支援総合事業と同様であること、特定福祉用具販売に係る費用の額に基準額が新設されること、登録施設介護サービス計画費等の額が100分の90であること、指定介護老人福祉施設等が指定を辞退できることとなること、地域ケア会議に他の法律に基づく会議との連携等の改正があること、介護保険事業計画の記載事項の号及び項が確定したこと（第117条第2項第3号・第4号、第3項第4号・第5号、第5項、第14項）である。あわせて、お示しいただいた記事の記述11件を原典により確かめ（一致8・一部一致1・確認できない2）、当たるものを計画素案に反映した。計画素案は21箇所を改めた</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -3385,19 +3385,19 @@
       <c r="A109" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
+          <t>第10期計画_社内作業ファイルの点検.xlsx</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>19施策の評価可能性の判定は受託者の基準による</t>
+          <t>社内の作業ファイル（令和8年9月8日。24シート）を当方の算定・受領資料・制度の定めと突き合わせた点検の記録。住民基本台帳の転記は18件中17件が一致し、不一致1件は美瑛町 令和8年の65〜74歳（高齢化率が3.64ポイント低く出る）。コーホート変化率法は8件の置き方のうち5件が不適合で、同じ資料で組み直すと65歳以上（3町計）は横ばいとなり当方の案Cと向き・水準が合う。地域密着型サービスの「要支援1〜要介護5まで〇」は制度とも実績とも合わないため年報の要介護度別の実績で埋める案を示している。認知症施策の評価の視点は都道府県分であり市町村分の6指標と別である。ご決定を要する事項は業務工程管理表へ移してある</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
+          <t>第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
+          <t>19施策の評価可能性の判定は受託者の基準による</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
+          <t>第10期計画_第9期施策別評価表と暫定評価ルール.xlsx</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
+          <t>評価ルールは暫定であり、発注者のご確認を要する。06シートに交付金の得点による19施策の暫定評価を加えた（割当ての確認を要する）</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -3460,19 +3460,19 @@
       <c r="A112" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
+          <t>第10期計画_第9期計画の評価・検証_中間報告.docx</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
+          <t>仕様書５の令和8年8月の提出物。第9期最終年度の実績が未確定のため、判定はいずれも中間判定である</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -3485,19 +3485,19 @@
       <c r="A113" s="6" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
+          <t>第10期計画_第9期評価の自己点検記録.xlsx</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
+          <t>受託者が自らの整理を批判的に検証した記録。作成過程の資料であり、送付資料としては用いない。不足資料の一覧（06シート）のみ「必要事項の一覧」に反映済み</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
+          <t>第10期計画_策定委員会資料_交付金評価結果.docx</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
+          <t>保険者機能強化推進交付金等の評価結果を策定委員会にお諮りするための資料。委員会に諮ること自体が交付金の要件であるため、評価結果は計画本文に載せず本資料に整理した。委員会にお諮りする事項6件を含む</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
+          <t>第10期計画_算定方法の整合確認_国と見える化.xlsx</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
+          <t>見込量算定と保険料試算の計算方法を国の様式及び見える化システムと対照したもの。地域支援事業費の範囲と調整交付金の算定基礎を修正し基本ケースは6,740円となった。補正（施策反映）の設計と確定を要する事項6件を含む</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -3560,19 +3560,19 @@
       <c r="A116" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_素案への加筆版の点検.xlsx</t>
+          <t>第10期計画_管理の統合と成果品の棚卸し.xlsx</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
+          <t>決定待ち以外の部分の再点検、確認事項の管理台帳の統合、役割を終えた成果品と誤りを正した記録の整理。作成に用いた処理101件のうち98件は作り直せ、残る3件は受領資料を作業領域から読むものである。確認事項は業務工程管理表140件と計画素案の別管理表60件の2か所にあり、同じ問いを二重に管理しているものが8件ある。施設・居住系の月平均利用者数は計画作成支援ツール（3町合計）と年報（保険者単位）で9.8％違う。算定又は記述に誤りがあり正したもの10件を、発見の経緯と再発を防ぐ手立てとともに記録している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3585,19 +3585,19 @@
       <c r="A117" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付実績データの受領点検.xlsx</t>
+          <t>第10期計画_素案への加筆版の点検.xlsx</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
+          <t>社内で計画素案に図と注記を加えた版（令和8年9月17日受領）の点検。加筆の土台が令和8年9月10日の素案（806段落130表36図）であり、以後の令和8年9月15日・16日の作業が入っていないため、そのまま差し替えると7日分が失われる。第6章の保険料は6,740円（旧）のままで、当方の最新（令和8年9月17日時点）は6,436円である。加筆はすべて第2章第1節への挿入で、図13点と「※（案）」の注記15件。削除はない。注記は計画素案の本文に確認事項を書かない方針に反するため、確認事項又は資料提供依頼として登録する。目次のページ番号が全50行とも1になっている。受領ファイルは作成者名がファイルの属性に含まれるため格納しない。差し替えではなく加筆分を最新版へ移す手順を8段階で示している</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
+          <t>第10期計画_給付実績データの受領点検.xlsx</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
+          <t>給付実績データ（資料No.23）の受領点検。個人情報の取扱いのご確認、代表KPI H15の算定、サービス別・要介護度別の実績、収録項目の範囲。加算・減算の内訳が収録されていないため代表KPI H16は算定できない</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
+          <t>第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
+          <t>令和8年9月25日受領資料4件の受領点検。3町の地域包括支援センター事業実施報告書（令和7年度）・実施計画書（令和8年度）と、令和7年度の給付費データ（広域連合単位）の再提供。確認事項No.87（令和7年度の給付費の差129,580,267円）は3町合計と広域連合単位が要介護度別まで円単位で一致し解決した。地域支援事業の量の令和7年度の実施状況（確認事項No.112）と認知症総合支援事業の取組の回数（確認事項No.150）を町別に整理した。給付費データの明細には氏名・生年月日・住所等を含むため集計値のみを収録している</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3660,19 +3660,19 @@
       <c r="A120" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
+          <t>第10期計画_給付適正化計画の位置づけと追加検討事項.xlsx</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
+          <t>令和8年9月10日に受領した5件の資料（進捗管理の手引き、交付金評価指標の市町村分・都道府県分、介護給付適正化の計画策定に関する指針、介護SCR）の内容を第10期計画に反映するための協議資料。第9期計画は施策4-3を「介護給付費の適正化（第6期給付適正化計画）」としており、第10期での位置づけを3案で比較した。ご指示により計画素案の本文には反映していない。ご判断をお願いする事項5件と、業務工程管理表に登録する確認事項4件を含む</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_要介護認定データの確認.xlsx</t>
+          <t>第10期計画_総合事業実施状況調査の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>見える化B系列の受領点検</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の受領点検。通いの場の実績、一般介護予防事業、サービス・活動事業。代表KPI H05の総合事業ベースの基準値の算定</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -3710,19 +3710,19 @@
       <c r="A122" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
+          <t>第10期計画_要介護認定データの確認.xlsx</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>見える化B系列の受領点検</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
+          <t>第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
+          <t>見える化システムの「推計方法の設定」画面で令和8年度の実績見込み値を編集するための数値。令和8年度は令和8年4月から7月までの4か月であり年度を代表しないため、令和7年度（12か月の完結年度）の月平均を置く案とした。差し替えるのは①認定者数・②施設・居住系サービス利用者数・③在宅サービス利用者数・④在宅サービス利用回（日）数の4画面である。①を差し替えないと利用率の分母が令和8年度のままになる。①〜④のいずれも年報（令和7年度）の様式1の5・様式1の6・様式1の7・様式2による確定値で、要介護度別に出している。要介護度別を12で除して足した値が見える化システムの総括表詳細（１）と全24サービスで一致することを検算した。入力欄は人数が整数・利用回（日）数が小数第1位までであることを確かめ、整数版（群ごとに合計を保つ最大剰余法）と小数第1位版を用意した。画面の令和7年度の整数をそのまま貼らない理由を4点示し、入力に併せて設定する項目も整理した。②③④はそのまま入力できる。①認定者数は編集する項目が画面にあるかを確かめられていないため、入力を始める前のご確認をお願いしている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
+          <t>第10期計画_見える化_入力箇所と入力値.xlsx</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
+          <t>見える化システムで推計を作り直す場合に、画面の値を変える箇所と、そこに入れる値だけを画面の順（手順1から手順8）にまとめたもの。全14シート。初期値のままでよい箇所は載せておらず、初期値であることを確かめる必要がある箇所のみ「確認」として区分を分けて掲げている。変更する箇所28件・設定の選択14件。人口の設定（案C。画面の入力欄165のうち改めるのは令和8年度以降の135）、令和8年度の実績見込み値（令和7年度の月平均への差し替え）、認定者数・施設居住系・在宅の利用者数・利用回（日）数（全8年度）、地域支援事業の量と事業費、所得段階別第1号被保険者数16段階・割合・基準所得金額を収めている。入力後に確かめる値（第1号被保険者数・認定者数・補正後被保険者数）と、上乗せ率と調整交付金の作り方の違いにより差が残る値も掲げた。画面ごとに入力の様式が違うため、施設・居住系は画面の3区分の並びによる利用者数、在宅は利用率（分母は認定者数−施設・居住系サービス利用者数）、利用回（日）数は1人1月あたり（延べではない。合計の列もない）、地域支援事業は量（手順6。4区分・令和6年度から令和11年度の6年度）と事業費（手順7。5群33項目）を画面ごとに分けている。様式は令和8年9月30日に受領した入力画面の写しによる（将来推計36点・利用回（日）数2点）。必要資料が未受領であることによる暫定値である</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3785,19 +3785,19 @@
       <c r="A125" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
+          <t>第10期計画_見える化_将来推計の設定資料の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
+          <t>令和8年9月11日に受領した見える化システムの将来推計の設定資料4ファイルの受領点検。4件はいずれも「将来推計」の「推計方法の設定」画面で認定率・在宅サービス利用率の伸びを選ぶための参考シートであり、施設・居住系サービス利用者数の伸びを設定するためのシートは含まれていない。当広域連合では推計誤差が算定されていないサービスが5件あり、うち施設・居住系に属するのは地域密着型特定施設入居者生活介護の1件である。推計誤差が大きいサービスは当方の対計画比の補正試算で「補正では解消しない外れ」とした6件のうち4件と一致する。あわせて令和8年9月11日に受領した画面の写し7点により、推計方法の設定が既定値のままであること（総人口は社人研推計、実績値は令和8年度、伸びの選択は3つとも0）、計画素案 第6章第2節の見込量表の出所が見える化システムの自然体推計値であること、システムが令和32年度まで推計することを確かめた。施設・居住系の画面から先へ進めない件の切り分けを示した（当方はシステムに接続できないため原因を特定したものではない）。ご判断・ご確認をお願いする事項7件を含む（うち1件は解決）</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3810,19 +3810,19 @@
       <c r="A126" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
+          <t>第10期計画_見える化_推計結果の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。必要資料が未受領であることによる暫定値であり確定値ではない。その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
+          <t>見える化システムで実際に推計した結果（推計パターン9028（１））を受領し、当方の算定と突き合わせて直す必要のある箇所を優先順に整理したもの。優先Aは、①地域支援事業費が全ての年度で0であること、②所得段階を弾力化しておらず標準13段階のままであること（当連合の条例は16段階）、③令和8年度の実績見込み値を編集していないこと（18区分が令和7年度と±10％を超えてずれ、うち4区分は0のまま令和9年度以降に残る）、④所得段階別の計が第10期と令和12年度以降とで別の人口系列によっていること（加入割合の合計が令和12年度以降で1.0を超える）の4件である。第9期の保険料基準額は見える化6,427.89円・当方の再現6,427.92円で一致しており、算定式そのものは同じものであることを確かめた。同じ出力の中に保険料基準額が2通り（1シート6,907.36円・5シート6,599.51円）あることも掲げている。受領したファイルは保管せず集計値のみを用いている。人口の設定を案Cに改める場合の入力値（総人口・男女別6階級・第2号被保険者の165欄）も07シートに掲げている。令和6年度・令和7年度は実績であるため画面の値をそのままとし、令和8年度以降を案Cに改めるもので、第1号被保険者数は令和11年度9,213人と当方の算定に一致する。08シートには「②保険料基準額に対する割合の弾力化」の画面に入れる基準所得金額（第7段階から第16段階の10件）と基準額に対する割合（16段階・公費軽減前・全年度共通）を掲げている。同画面には所得段階別第1号被保険者数が既に入力されており、全8年度・全16段階で当方の値と一致するため入れ直しを要しない。09シートは人口の設定を案Cに改めた後の再出力の点検であり、第1号被保険者数と調整交付金は案Cに変わった一方、認定者数・総給付費・標準給付費見込額は改める前の出力と1円も変わっていないこと（給付費の側へ及んでいないこと）を示す。10シートは将来推計ワーニングチェック結果39件の点検であり、施策反映の3画面は該当無し、39件のうち18件（訪問介護）は当区域の実態、21件は令和8年度の実績見込み値と1人1月あたり給付費の年度による</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化_見込量の入力値（暫定）.xlsx</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計へ入力する令和9年度以降のサービス見込量の値。必要資料が未受領であることによる暫定値であり確定値ではない。その旨を00シート・各シートの表題・注記・印刷のフッターに明記している。認定者数、施設・居住系サービス利用者数（8区分）、在宅サービス利用者数（21区分）、在宅サービス利用回（日）数（12区分）を要介護度別に掲げ、令和9年度から令和11年度に加えて令和17年度・令和22年度も出している。利用回（日）数は令和8年9月30日に受領した画面の写しにより1人1月あたりに改めた（延べではなく、合計の列もない）。利用者数は整数、利用回（日）数は小数第1位で、利用者数は要支援の群・要介護の群ごとに合計を保つ最大剰余法により配分している（単純に四捨五入すると定期巡回のような小口のサービスが0になり、令和9年度以降も0のまま残る）。要支援の列があるかどうかは受領した画面の写しから読んでおり、年報に実績がないことと突き合わせている。値を入れる前に選ぶ設定（実績見込み値の編集・伸びの選択）と当方の案も併せて掲げた。暫定である理由を、受託者の側で確定できるもの4件、発注者・3町の資料待ちであるが届かなければ据え置きのまま確定するもの15件、国の告示・公布を待つもの4件に分けて示している。当方の29区分と入力画面の45区分は束ね方が違い、区分一覧そのものを受領していないため、要支援の列と要介護の列を分けてどちらにも貼れる形にしている。ご判断をお願いする事項（総人口の設定・実績見込み値の編集・伸びの選択・1人1月あたり給付費の年度）を含む</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -3860,19 +3860,19 @@
       <c r="A128" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化の指標（B5・B6・D49）の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>令和8年10月19日に受領した見える化システムの指標5件（B5-a 調整済み認定率（要介護度別）・B5-c 同（要支援除く）・B6-a 調整済み重度認定率・B6-b 調整済み軽度認定率・D49 地域差指数の指標の解説）を当方の収録値及び計画素案と突き合わせたもの。資料提供依頼No.1・No.16に当たる。既に収録していた221件は差異なく一致し、令和8年3月末の値（重度5.2％・軽度13.2％・合計18.4％）を加えた。重度は低下が続き、軽度は令和5年3月末を底に上昇した後は横ばいである。一方、当方が「他地域と比較」の出力から収録していた系列は本広域連合の値と全ての時点で異なり、どの地域の行であるのかを特定できていないことが分かった（確認事項No.190）。計画素案 第3章第4節2がこの系列の値を本広域連合の値として掲げていたため3箇所を是正した。D49の解説により、受給率の分母が第1号被保険者数であることが原典で確定し（修正指示A-11の留保が解消）、4指標のうち性・年齢調整後であるのは2指標だけであるため地域差指数を乗法的に分解できないことが分かった（上川管内21保険者で受給率×受給者単価と給付月額の差は▲0.473から＋0.416）。</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -3885,19 +3885,19 @@
       <c r="A129" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3910,19 +3910,19 @@
       <c r="A130" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3935,19 +3935,19 @@
       <c r="A131" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3960,19 +3960,19 @@
       <c r="A132" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3985,19 +3985,19 @@
       <c r="A133" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4060,19 +4060,19 @@
       <c r="A136" s="6" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4110,19 +4110,19 @@
       <c r="A138" s="6" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4160,19 +4160,19 @@
       <c r="A140" s="6" t="n">
         <v>136</v>
       </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -4185,19 +4185,19 @@
       <c r="A141" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -4260,19 +4260,19 @@
       <c r="A144" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -4285,19 +4285,19 @@
       <c r="A145" s="6" t="n">
         <v>141</v>
       </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -4310,136 +4310,186 @@
       <c r="A146" s="6" t="n">
         <v>142</v>
       </c>
-      <c r="B146" s="9" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画_送付資料一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
         <is>
           <t>内部保管</t>
         </is>
       </c>
-      <c r="C146" s="7" t="inlineStr">
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
         <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D146" s="7" t="inlineStr">
+      <c r="D148" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="28" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B151" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C151" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr"/>
-      <c r="E149" s="4" t="inlineStr"/>
-    </row>
-    <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="C150" s="7" t="inlineStr">
+      <c r="D151" s="4" t="inlineStr"/>
+      <c r="E151" s="4" t="inlineStr"/>
+    </row>
+    <row r="152" ht="26" customHeight="1">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="inlineStr"/>
-      <c r="E150" s="7" t="inlineStr"/>
-    </row>
-    <row r="151" ht="26" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
-        </is>
-      </c>
-      <c r="D151" s="7" t="inlineStr"/>
-      <c r="E151" s="7" t="inlineStr"/>
-    </row>
-    <row r="152" ht="26" customHeight="1">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr"/>
       <c r="E152" s="7" t="inlineStr"/>
     </row>
     <row r="153" ht="26" customHeight="1">
-      <c r="A153" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B153" s="6" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr"/>
       <c r="E153" s="7" t="inlineStr"/>
     </row>
     <row r="154" ht="26" customHeight="1">
-      <c r="A154" s="12" t="inlineStr">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>納品時又は求めに応じて提出する</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr"/>
+      <c r="E154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155" ht="26" customHeight="1">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr"/>
+      <c r="E155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156" ht="26" customHeight="1">
+      <c r="A156" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B154" s="13" t="n">
-        <v>142</v>
-      </c>
-      <c r="C154" s="14" t="inlineStr"/>
-      <c r="D154" s="14" t="inlineStr"/>
-      <c r="E154" s="14" t="inlineStr"/>
-    </row>
-    <row r="156" ht="76" customHeight="1">
-      <c r="A156" s="11" t="inlineStr">
+      <c r="B156" s="13" t="n">
+        <v>144</v>
+      </c>
+      <c r="C156" s="14" t="inlineStr"/>
+      <c r="D156" s="14" t="inlineStr"/>
+      <c r="E156" s="14" t="inlineStr"/>
+    </row>
+    <row r="158" ht="76" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4449,8 +4499,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A148:E148"/>
-    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A158:E158"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_成果品の送付区分表.xlsx
+++ b/output/第10期計画_成果品の送付区分表.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3885,19 +3885,19 @@
       <c r="A129" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
+          <t>第10期計画_見える化システムからご出力をお願いする資料.xlsx</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
+          <t>見える化システムの将来推計機能・事業所分析機能・人口メッシュ表示機能はいずれも都道府県及び市区町村の職員専用の機能であり、受託者のアカウントでは操作できない。同システムからご出力いただければ解ける事項を13件の資料として一覧とし、機能・画面の順路・出力の形式・範囲・何が確かめられるか・関係する確認事項を対にしたもの。画面の順路と出力の形式は、公表されている地域分析の手引き（令和8年9月改訂版）、第10期の新機能のリーフレット及び同システムのお知らせにより確かめている。優先A4件（事業所分析データ・利用マニュアル・将来推計の再出力・介護保険事業状況報告の設定の画面）、優先B7件、優先C2件。原典により新たに分かったことを14件掲げ、うち令和8年度の実績見込みの期間（令和8年5月から）と地域支援事業費の定義（対象経費支出予定額）は当方の整理と食い違うため確認事項No.191・No.192として登録した。</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -3910,19 +3910,19 @@
       <c r="A130" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
+          <t>第10期計画_見える化データの受領点検_福祉用具住宅改修とリハ.xlsx</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
+          <t>介護保険最新情報Vol.1521「介護給付適正化における住宅改修等の点検および福祉用具購入・貸与調査の取組促進について」の観点から、令和8年9月10日に受領した見える化システムの個別指標99件（値あり87件・値なし12件）を点検したもの。福祉用具貸与8種目の全国比較、リハビリテーション専門職の配置状況、リハビリテーション関係の加算の算定状況、交付金評価のエ・オ2項目（各8点）の取得可能性。成果品への反映6件のうち4件は計画素案への反映の可否をお諮りする</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -3935,19 +3935,19 @@
       <c r="A131" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
+          <t>第10期計画_見える化入力マニュアルの点検と整合確認.xlsx</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
+          <t>社内で作成された全国自治体共通版の見える化システム簡易入力シート（5シート・615項目・徴求資料107件）と入力手順書（全9STEP）の点検、及び当方の見込量算定との整合確認。様式としての作りは妥当であり、手順が見える化システムの画面順と一致し、手順書が示すNo.の範囲は入力シートの手順別件数と1件の差もなく一致する。⑤保険料推計の算式は当方の保険料算定式と等価で、当方の値を入れると算定上の月額を小数第4位まで再現する。本件に当てはめるには手当てを要する点を13件挙げた。重いものは、人口系列を案Cに改めないと手順3から5の148項目の前提が崩れること、保険者機能強化推進交付金等の交付見込額で二重控除になるおそれがあること、低所得者軽減公費を別建てすると二重計上になること、広域連合を想定していないこと、担当者名・連絡先を求める欄が発注者指示と衝突することである。615項目を当方で埋まる137・資料待ち151・ご判断と未算定140・空欄と確認操作187に分けた。見える化システムが求める8年度のうち令和12・27・32年度の99項目は当方が未算定であるが、人口の基礎は令和32年度まであるため算定を広げられる。受領ファイルはファイルの属性に作成者名があるため格納していない。ご判断をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -3960,19 +3960,19 @@
       <c r="A132" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
+          <t>第10期計画_見える化総括表の受領点検.xlsx</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
+          <t>見える化システムの総括表・管理指標グラフの受領点検。第9期（令和6・7年度）の対計画比、サービス別の乖離、保険料基準額の計画と実績、代表KPI H15の基準値、読み方の注意6点</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -3985,19 +3985,19 @@
       <c r="A133" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
+          <t>第10期計画_見込量の季節性の検証と施策反映の設計.xlsx</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
+          <t>令和8年度が年度途中であること、冬季と夏季で事業内容・給付費が異なる可能性が高いことを踏まえ、数値の補正方法とKPI達成を目的とした施策反映を検討したもの。冬季と夏季の差は施設＋2.80％・在宅▲2.48％と実測できたが、給付費で加重すると相殺され、採用パターン（令和7年度基準）では季節補正の効きは0円である。令和8年度は月報により4か月と確定した。ご判断をお願いする事項4件と、確認をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4010,19 +4010,19 @@
       <c r="A134" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
+          <t>第10期計画_見込量算定に要する資料と電話照会の進め方.docx</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
+          <t>サービス見込量の算定に要する資料の一覧、資料が届かない場合の当方の扱い（既定値23件）、及び電話で照会するときの言い方の例。確認事項No.87（給付費データ 令和7年度の3町計と広域連合単位の差）について突き合わせた事実を手元資料としてまとめている。本件は令和8年9月25日に令和7年度のファイルの再提供を受けて解決した（3か年とも要介護度別まで円単位で一致する）。担当者名・電話番号は記入枠としている</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4035,19 +4035,19 @@
       <c r="A135" s="6" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の別管理表.xlsx</t>
+          <t>第10期計画_計画策定の進捗と今後の確認事項.docx</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
+          <t>令和8年10月2日のご照会への回答。実施済み調査 結果報告書の計画策定全体における位置づけ、調査分析として今後修正・追加を予定している事項、ご確認・ご判断をお願いする事項（保険料の月額を動かすものと法定記載事項に直結するものに絞ったもの）、広域連合又は構成3町で追加確認・資料提供が必要な事項、今後の作成・協議スケジュール、次回協議までの受託者・広域連合・構成3町それぞれの対応事項及び未確定事項をどの資料のどこで管理しているかを1冊にまとめたもの。未確定事項の台帳は業務工程管理表と実施済み3調査の受領点検と集計によっており、本資料は新たな台帳を起こしていない</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4060,19 +4060,19 @@
       <c r="A136" s="6" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
+          <t>第10期計画_計画素案の別管理表.xlsx</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
+          <t>素案本文の未確定箇所の一覧。確認をお願いする事項が中心である</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4085,19 +4085,19 @@
       <c r="A137" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_計画素案の課題整理.xlsx</t>
+          <t>第10期計画_計画素案の記載内容の洗い出しと対比.xlsx</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
+          <t>計画素案の章節構成を洗い出し、介護保険法第117条第2項・第3項の記載事項、国の第10期基本指針（案）別表「確認すべき指標・状況」11事項、令和8年3月の全国介護保険・高齢者保健福祉担当課長会議資料の3つの原典と対比したもの。対比により見つかった記載漏れ11件を計画素案へ加えた（調整交付金の年齢区分の7区分化、保険料段階の基準額82.65万円、補足給付の見直し、令和8年度介護報酬改定、一定以上所得基準ほか）。あわせて、本文の【　】の小見出し68件を法令が求める事項の説明・第9期計画にもある事項・第9期計画になく法令も直接には求めていない分析の3つに区分し、計画に残すか打合せ協議用の資料へ移すかを判定している。第9期計画にない体裁10件についても取扱いを示した</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4117,12 +4117,12 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
+          <t>第10期計画_計画素案の課題整理.xlsx</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
+          <t>計画素案の未確定箇所と確認事項を突き合わせた課題整理。未確定箇所は計画素案そのものを、確認事項は業務工程管理表を数えているため、いずれかを更新すれば本表も追随する。未確定は第6章第4節（施設の見込み）に集中している。第1次概算（9月26日）を止めている確認事項について、決着しない場合の当方の扱い（既定値）を全件に置いた。未確定箇所とは別に、書くべき内容がまだ入っていない節を示している。ご判断をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
+          <t>第10期計画_認定率の年齢調整分析.xlsx</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
+          <t>年齢調整の方法と結果。従前の記述を改めた経緯を含む</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4160,19 +4160,19 @@
       <c r="A140" s="6" t="n">
         <v>136</v>
       </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査クロス集計・分析.xlsx</t>
+          <t>第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>集計値のみを収録している（個票は収録していない）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）の検討資料。位置づけは3案を比較し、構成3町がそれぞれ策定し広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案Bを採用した（令和8年9月16日）。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みで、新たな節・章は起こしていない。確認事項No.130の②（実施主体）・③（意見の聴取）は決着していない。同法の名宛人は「市町村」であり、広域連合が一体のものとして定めても市町村計画としての効力は生じない。認知症の人及び家族等からの意見の聴取は、手元に意見を聴いた資料がないことを確かめ、方法3案と時期を示した。見込量は給付サービス2種別を算定済みで、認知症総合支援事業（包括的支援事業）の量だけが立たない。認知症対応型共同生活介護の令和4年度の落ち込みは定員の縮小によるものであり趨勢ではないことを実測で示した。同法の条文を受領していないため項番号・文言は［要確認］としている。ご判断をお願いする事項4件、確認をお願いする事項2件、資料のご提供をお願いする事項2件を含む</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -4185,19 +4185,19 @@
       <c r="A141" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="B141" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
+          <t>第10期計画_調査クロス集計・分析.xlsx</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
+          <t>集計値のみを収録している（個票は収録していない）</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
+          <t>第10期計画_調査結果と年報実績の突合クロス集計.xlsx</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
+          <t>調査の結果と年報（令和7年度）の実績との突合。令和8年9月11日に年報の要介護度別の明細を収めたことにより初めて可能になった集計である。①在宅生活改善調査の要介護度分布は在宅の認定者の分布と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の認定者全体を代表しない。②居所変更実態調査の在籍者と年報の受給者は一致せず、介護老人保健施設だけが在籍＞受給である。特別養護老人ホーム等は受給者が回答施設の定員を上回り、区域を越えた施設利用が双方向に成立している。アンケート関係の成果品7件のうち6件を再出力した状況も収めている。ご判断・ご確認をお願いする事項3件を含む</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -4235,19 +4235,19 @@
       <c r="A143" s="6" t="n">
         <v>139</v>
       </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
+          <t>第10期計画_資料を受領できない場合のサービス見込量.docx</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>資料提供のご依頼</t>
+          <t>追加の資料が届かない前提でのサービス見込量。サービス見込量の算定 第1次概算（令和8年9月16日）がそのまま「資料が届かない前提」の見込量であることを示し、29サービスの見込量・12区分の利用回（日）数・地域支援事業の量・給付費・保険料・必要利用定員総数・中長期推計を掲げている。総給付費（3か年計）9,035,114,142円、算定上の月額基準額6,438円、百円未満四捨五入した保険料基準額6,400円（第9期と同額）。据え置き23件を、受託者の側で確定できるもの4件、発注者・3町の資料が届かなければ据え置きで確定するもの15件、国の告示・公布を待つもの4件に分けている。6,438円は据え置き前提の下限に近く、単価の趨勢や報酬改定を織り込むと基準額は6,500円から6,800円となる。ご判断をお願いする事項（単価の置き方。確認事項No.137）を含む</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -4260,19 +4260,19 @@
       <c r="A144" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="B144" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
+          <t>第10期計画_資料提供依頼_第9期の施策事業実績.xlsx</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
+          <t>資料提供のご依頼</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -4285,19 +4285,19 @@
       <c r="A145" s="6" t="n">
         <v>141</v>
       </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_追加調査報告書.xlsx</t>
+          <t>第10期計画_趨勢に現れない要因の分析.xlsx</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>追加で実施した調査の報告</t>
+          <t>国の第10期基本指針（案）と北海道第9期計画の8基本目標から、過去の実績の趨勢に現れない要因を12件抽出して分析したもの。認知症施策（自立度Ⅱ以上の割合は65.4％から60.3％へ低下）、高齢者向け住まい（介護保険の指定を受けないもの339人・戸は在宅受給者の34.2％）、給付適正化との整合（対象は総給付費の7.70％）、令和9年度の報酬改定（単価指数は7年で＋12.93％。改定のあった年となかった年で差が見られない）。ご判断をお願いする事項3件と、確認・ご提供をお願いする事項4件を含む</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>第10期計画_送付資料一覧.xlsx</t>
+          <t>第10期計画_追加調査報告書.xlsx</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
+          <t>追加で実施した調査の報告</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -4335,19 +4335,19 @@
       <c r="A147" s="6" t="n">
         <v>143</v>
       </c>
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+          <t>第10期計画_送付資料一覧.xlsx</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>計画素案の修正の作業記録</t>
+          <t>今回送付する資料の一覧と、ご確認・ご決定をお願いする事項</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
@@ -4367,129 +4367,154 @@
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
+          <t>第10期計画素案_修正指示書_令和8年7月.xlsx</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>計画素案の修正の作業記録</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
           <t>第10期計画素案_修正指示書_令和8年8月.xlsx</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr">
         <is>
           <t>計画素案の修正の作業記録</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t>【区分別の件数】</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="28" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
+    <row r="152" ht="28" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>取扱い</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr"/>
-      <c r="E151" s="4" t="inlineStr"/>
-    </row>
-    <row r="152" ht="26" customHeight="1">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>送付</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="C152" s="7" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr"/>
+    </row>
+    <row r="153" ht="26" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>送付</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
         <is>
           <t>そのまま送付する</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr"/>
-      <c r="E152" s="7" t="inlineStr"/>
-    </row>
-    <row r="153" ht="26" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>条件付き</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="C153" s="7" t="inlineStr">
-        <is>
-          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr"/>
       <c r="E153" s="7" t="inlineStr"/>
     </row>
     <row r="154" ht="26" customHeight="1">
-      <c r="A154" s="9" t="inlineStr">
-        <is>
-          <t>内部保管</t>
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="B154" s="6" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>納品時又は求めに応じて提出する</t>
+          <t>お諮りする内容である旨を明示して送付する</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr"/>
       <c r="E154" s="7" t="inlineStr"/>
     </row>
     <row r="155" ht="26" customHeight="1">
-      <c r="A155" s="10" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>内部保管</t>
         </is>
       </c>
       <c r="B155" s="6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>本業務の成果品ではない</t>
+          <t>納品時又は求めに応じて提出する</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr"/>
       <c r="E155" s="7" t="inlineStr"/>
     </row>
     <row r="156" ht="26" customHeight="1">
-      <c r="A156" s="12" t="inlineStr">
+      <c r="A156" s="10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>本業務の成果品ではない</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr"/>
+      <c r="E156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157" ht="26" customHeight="1">
+      <c r="A157" s="12" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B156" s="13" t="n">
-        <v>144</v>
-      </c>
-      <c r="C156" s="14" t="inlineStr"/>
-      <c r="D156" s="14" t="inlineStr"/>
-      <c r="E156" s="14" t="inlineStr"/>
-    </row>
-    <row r="158" ht="76" customHeight="1">
-      <c r="A158" s="11" t="inlineStr">
+      <c r="B157" s="13" t="n">
+        <v>145</v>
+      </c>
+      <c r="C157" s="14" t="inlineStr"/>
+      <c r="D157" s="14" t="inlineStr"/>
+      <c r="E157" s="14" t="inlineStr"/>
+    </row>
+    <row r="159" ht="76" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
         <is>
           <t>注1）「対象外」の5件は、他計画（障がい福祉計画・こども計画）を含む様式部品であり、本業務の成果品一覧には参考として掲げているものです。
 注2）区分は受託者の整理です。発注者において別の取扱いをご希望の場合はお申し付けください。特に「内部保管」としたものについて、ご確認をご希望の場合はそのまま提出します。</t>
@@ -4499,8 +4524,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A150:E150"/>
-    <mergeCell ref="A158:E158"/>
+    <mergeCell ref="A151:E151"/>
+    <mergeCell ref="A159:E159"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
